--- a/business-libraries/test-data/class_system/tool.xlsx
+++ b/business-libraries/test-data/class_system/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AJ7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,96 +430,102 @@
         <v>严重度*</v>
       </c>
       <c r="J1" t="str">
-        <v>对应归因*</v>
+        <v>对应归因编码*</v>
       </c>
       <c r="K1" t="str">
+        <v>对应归因名称</v>
+      </c>
+      <c r="L1" t="str">
         <v>工具标签*</v>
       </c>
-      <c r="L1" t="str">
-        <v>作用维度</v>
-      </c>
       <c r="M1" t="str">
+        <v>作用维度编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>效果说明</v>
+      </c>
+      <c r="O1" t="str">
         <v>操作步骤摘要*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>关键话术</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>预期效果*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>单次耗时</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>疗程与频次</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>重评间隔天数</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>禁止事项*</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>禁忌说明</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>前置工具编码</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>替代工具编码</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>进阶工具编码</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>证据等级*</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>证据来源</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>效果指标</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>失败标准</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>准备事项</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>所需材料</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>输出物</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>协同工具编码</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>版本*</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>C_RX_001</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B2" t="str">
-        <v>班会引导框架</v>
+        <v>班级目标里程碑拆解表</v>
       </c>
       <c r="C2" t="str">
-        <v>班会引导</v>
+        <v>目标拆解</v>
       </c>
       <c r="D2" t="str">
         <v>class_system</v>
       </c>
       <c r="E2" t="str">
-        <v>exercise</v>
+        <v>worksheet</v>
       </c>
       <c r="F2" t="str">
         <v>all</v>
@@ -528,102 +534,111 @@
         <v>teacher</v>
       </c>
       <c r="H2" t="str">
-        <v>感到情绪即将失控、疲惫难以恢复时</v>
+        <v>学生说不出班级目标，或目标只停留在口号</v>
       </c>
       <c r="I2" t="str">
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>纪律与凝聚力双低</v>
+        <v>CS_AT_GOAL</v>
       </c>
       <c r="K2" t="str">
-        <v>class_system,orange,discipline</v>
+        <v>目标系统未落地</v>
       </c>
       <c r="L2" t="str">
-        <v>情绪恢复</v>
+        <v>class_system,goal</v>
       </c>
       <c r="M2" t="str">
-        <v>1) 离开当前情境 2) 三轮缓慢呼吸 3) 命名情绪 4) 选最小行动</v>
+        <v>CS_GOAL</v>
       </c>
       <c r="N2" t="str">
-        <v>现在先停三分钟，这三分钟只属于你自己。</v>
-      </c>
-      <c r="O2" t="str">
-        <v>单次可下降 1-2 分主观压力值</v>
+        <v>把抽象目标转成可观察的阶段成果</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">和学生一起用一句话说清本学期班级要成为什么样
+把这句话拆成三个可观察的里程碑
+为第一个里程碑写清完成标准和检查时间
+贴在教室并每两周对照一次</v>
       </c>
       <c r="P2" t="str">
-        <v>3 分钟</v>
+        <v>我们这学期只做好一件事，你们觉得应该是哪一件？</v>
       </c>
       <c r="Q2" t="str">
-        <v>每日 1-2 次，连续 7 天</v>
+        <v>学生能复述目标和第一个里程碑</v>
       </c>
       <c r="R2" t="str">
-        <v>7</v>
+        <v>一节班会</v>
       </c>
       <c r="S2" t="str">
-        <v>不用于替代危机处置；出现自伤念头或持续失眠时须转介心理专员</v>
+        <v>每学期一次</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>不要由教师单方面宣布目标</v>
       </c>
       <c r="V2" t="str">
         <v/>
       </c>
       <c r="W2" t="str">
-        <v>C_RX_004</v>
+        <v/>
       </c>
       <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
         <v>B</v>
       </c>
-      <c r="Y2" t="str">
-        <v>Kabat-Zinn 正念减压研究；教师群体适应性改编研究（2023）</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>主观压力值下降&gt;=1分；一周后情绪耗竭维度得分下降</v>
-      </c>
       <c r="AA2" t="str">
-        <v>连续使用3次后主观压力值未下降</v>
+        <v>班级系统建设手册 第2章</v>
       </c>
       <c r="AB2" t="str">
-        <v>确保教师有3分钟不被打扰的环境</v>
+        <v>随机抽问三名学生能说出目标</v>
       </c>
       <c r="AC2" t="str">
-        <v>计时器、一周能量记录卡</v>
+        <v>两周后仍无人能复述</v>
       </c>
       <c r="AD2" t="str">
-        <v>一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE2" t="str">
-        <v>C_RX_004</v>
+        <v>记录表</v>
       </c>
       <c r="AF2" t="str">
-        <v>班级系统建设处方库 P12</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AI2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH2" t="str">
-        <v>class_system,home_school</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>C_RX_002</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B3" t="str">
-        <v>小组积分制</v>
+        <v>班级事务 SOP 卡</v>
       </c>
       <c r="C3" t="str">
-        <v>小组积分</v>
+        <v>事务SOP</v>
       </c>
       <c r="D3" t="str">
         <v>class_system</v>
       </c>
       <c r="E3" t="str">
-        <v>worksheet</v>
+        <v>checklist</v>
       </c>
       <c r="F3" t="str">
         <v>all</v>
@@ -632,46 +647,49 @@
         <v>teacher</v>
       </c>
       <c r="H3" t="str">
-        <v>日常自我照顾和压力管理</v>
+        <v>班级事务过度集中在教师身上</v>
       </c>
       <c r="I3" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>班级氛围偏低</v>
+        <v>CS_AT_ORG</v>
       </c>
       <c r="K3" t="str">
-        <v>class_system,yellow,motivation</v>
+        <v>组织系统缺位</v>
       </c>
       <c r="L3" t="str">
-        <v>自我照顾</v>
+        <v>class_system,org</v>
       </c>
       <c r="M3" t="str">
-        <v>1) 记录每日能量变化 2) 识别能量消耗源 3) 制定能量补充计划</v>
+        <v>CS_ORG</v>
       </c>
       <c r="N3" t="str">
-        <v>记录本身就是一种觉察和关爱。</v>
-      </c>
-      <c r="O3" t="str">
-        <v>帮助教师建立自我照顾习惯，降低日常压力水平</v>
+        <v>把日常事务转成学生可独立执行的流程</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">选一个每天都发生的事务（如晨检、放学清扫）
+写清责任人、执行步骤、异常处理和复盘时间
+让学生试运行三天，教师只观察不介入
+第四天复盘，只调整卡住的那一步</v>
       </c>
       <c r="P3" t="str">
-        <v>5 分钟</v>
+        <v>这件事从明天起由你负责，遇到处理不了的情况再来找我。</v>
       </c>
       <c r="Q3" t="str">
-        <v>每日一次，持续 14 天</v>
+        <v>该事务连续一周无需教师介入</v>
       </c>
       <c r="R3" t="str">
-        <v>14</v>
+        <v>30 分钟</v>
       </c>
       <c r="S3" t="str">
-        <v>本工具不适用于危机情境；教师处于急性心理危机时请先转介心理专员</v>
+        <v>每两周新增一项</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U3" t="str">
-        <v/>
+        <v>不要同时铺开多个 SOP；一次只做一项</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -680,48 +698,54 @@
         <v/>
       </c>
       <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
         <v>B</v>
       </c>
-      <c r="Y3" t="str">
-        <v>教师自我效能感训练研究（2022）</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>连续一周能量记录完整且主观压力值下降</v>
-      </c>
       <c r="AA3" t="str">
-        <v>连续3天未记录</v>
+        <v>班级系统建设手册 第3章</v>
       </c>
       <c r="AB3" t="str">
-        <v>打印一周能量记录卡</v>
+        <v>连续 5 天无需教师提醒</v>
       </c>
       <c r="AC3" t="str">
-        <v>一周能量记录卡、笔</v>
+        <v>试运行三天内出现两次以上中断</v>
       </c>
       <c r="AD3" t="str">
-        <v>完成的一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE3" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF3" t="str">
-        <v>班级系统建设处方库 P15</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AI3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>C_RX_003</v>
+        <v>CS_RX_003</v>
       </c>
       <c r="B4" t="str">
-        <v>冲突调解话术</v>
+        <v>十分钟班级微复盘</v>
       </c>
       <c r="C4" t="str">
-        <v>冲突调解</v>
+        <v>微复盘</v>
       </c>
       <c r="D4" t="str">
         <v>class_system</v>
@@ -736,46 +760,49 @@
         <v>teacher</v>
       </c>
       <c r="H4" t="str">
-        <v>需要同伴支持和经验交流时</v>
+        <v>活动办完就结束，经验无法沉淀</v>
       </c>
       <c r="I4" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>班级氛围偏低</v>
+        <v>CS_AT_ACTIVITY</v>
       </c>
       <c r="K4" t="str">
-        <v>class_system,orange,conflict</v>
+        <v>活动系统空转</v>
       </c>
       <c r="L4" t="str">
-        <v>同伴支持</v>
+        <v>class_system,activity</v>
       </c>
       <c r="M4" t="str">
-        <v>1) 邀请2-3位同事 2) 轮流分享当前困扰 3) 团体生成至少一条行动建议</v>
+        <v>CS_ACTIVITY</v>
       </c>
       <c r="N4" t="str">
-        <v>你不是一个人在战斗。</v>
-      </c>
-      <c r="O4" t="str">
-        <v>通过结构化同伴支持缓解教师的孤立感</v>
+        <v>把活动经验转成可重复的改进</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">活动结束当天，留出十分钟
+每人说一个「下次要保留的动作」
+每人说一个「下次要调整的动作」
+教师只记录不评价，把结果贴在班级角</v>
       </c>
       <c r="P4" t="str">
-        <v>30 分钟</v>
+        <v>今天我们只讨论一件事：哪个环节帮助大家更稳定，哪个环节明天需要调整。</v>
       </c>
       <c r="Q4" t="str">
-        <v>每周一次，持续 4 周</v>
+        <v>形成至少两条下次可执行的改进</v>
       </c>
       <c r="R4" t="str">
-        <v>28</v>
+        <v>10 分钟</v>
       </c>
       <c r="S4" t="str">
-        <v>本活动不等同于心理治疗，涉及严重心理问题时应转介专业支持</v>
+        <v>每次活动后</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U4" t="str">
-        <v/>
+        <v>教师不要在复盘中先发表意见</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -784,54 +811,60 @@
         <v/>
       </c>
       <c r="X4" t="str">
-        <v>C</v>
+        <v/>
       </c>
       <c r="Y4" t="str">
-        <v>同伴支持对教师职业倦怠干预效果研究（2021）</v>
+        <v/>
       </c>
       <c r="Z4" t="str">
-        <v>参与教师反馈压力感和孤立感下降</v>
+        <v>B</v>
       </c>
       <c r="AA4" t="str">
-        <v>连续2次参与人数低于2人</v>
+        <v>班级系统建设手册 第4章</v>
       </c>
       <c r="AB4" t="str">
-        <v>准备问题引导卡</v>
+        <v>产出 &gt;= 2 条具体改进</v>
       </c>
       <c r="AC4" t="str">
-        <v>问题引导卡、白板、记号笔</v>
+        <v>学生只说「挺好的」</v>
       </c>
       <c r="AD4" t="str">
-        <v>行动建议记录表</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE4" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF4" t="str">
-        <v>班级系统建设处方库 P20</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AI4" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>C_RX_004</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="B5" t="str">
-        <v>班级文化建设方案</v>
+        <v>规则共构工作坊</v>
       </c>
       <c r="C5" t="str">
-        <v>班级文化</v>
+        <v>规则共构</v>
       </c>
       <c r="D5" t="str">
         <v>class_system</v>
       </c>
       <c r="E5" t="str">
-        <v>script</v>
+        <v>framework</v>
       </c>
       <c r="F5" t="str">
         <v>all</v>
@@ -840,46 +873,49 @@
         <v>teacher</v>
       </c>
       <c r="H5" t="str">
-        <v>出现明显负面自动思维时</v>
+        <v>规则只贴在墙上，学生不认同</v>
       </c>
       <c r="I5" t="str">
         <v>medium</v>
       </c>
       <c r="J5" t="str">
-        <v>纪律与凝聚力双低</v>
+        <v>CS_AT_ENV</v>
       </c>
       <c r="K5" t="str">
-        <v>class_system,green,culture</v>
+        <v>环境系统薄弱</v>
       </c>
       <c r="L5" t="str">
-        <v>认知调整</v>
+        <v>class_system,environment</v>
       </c>
       <c r="M5" t="str">
-        <v>1) 识别负面自动思维 2) 检验思维的证据 3) 生成替代性解释 4) 行动计划</v>
+        <v>CS_ENV</v>
       </c>
       <c r="N5" t="str">
-        <v>想法不一定是事实，让我们一起来看看证据。</v>
-      </c>
-      <c r="O5" t="str">
-        <v>帮助教师识别和调整负面自动思维，降低认知层面的压力</v>
+        <v>把规则从教师要求转成共同约定</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">挑一条最常被违反的规则
+让学生说出这条规则存在的理由，教师补充缺失的部分
+一起把规则改写成可观察的行为描述
+约定试行两周后复盘</v>
       </c>
       <c r="P5" t="str">
-        <v>15 分钟</v>
+        <v>这条规则不是为了限制大家，而是为了让学习和相处更可预期。我们先试行三天再复盘。</v>
       </c>
       <c r="Q5" t="str">
-        <v>每周 2-3 次，持续 4 周</v>
+        <v>该规则违反次数下降 50% 以上</v>
       </c>
       <c r="R5" t="str">
-        <v>14</v>
+        <v>一节班会</v>
       </c>
       <c r="S5" t="str">
-        <v>有严重抑郁症状的教师应先在心理专员指导下使用</v>
+        <v>每月一条</v>
       </c>
       <c r="T5" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U5" t="str">
-        <v/>
+        <v>不要一次重构全部规则</v>
       </c>
       <c r="V5" t="str">
         <v/>
@@ -888,49 +924,281 @@
         <v/>
       </c>
       <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
         <v>B</v>
       </c>
-      <c r="Y5" t="str">
-        <v>Beck 认知疗法教师适应性改编研究（2022）</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>2周后负面自动思维频率下降 &gt;=30%</v>
-      </c>
       <c r="AA5" t="str">
-        <v>使用2周后负面思维频率未下降且教师反馈无改善</v>
+        <v>班级系统建设手册 第5章</v>
       </c>
       <c r="AB5" t="str">
-        <v>打印认知重构工作表</v>
+        <v>两周内违反次数明显下降</v>
       </c>
       <c r="AC5" t="str">
-        <v>认知重构工作表、笔</v>
+        <v>两周后无变化</v>
       </c>
       <c r="AD5" t="str">
-        <v>完成的认知重构工作表</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE5" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF5" t="str">
-        <v>班级系统建设处方库 P18</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AI5" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH5" t="str">
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>CS_RX_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>冲突修复四步法</v>
+      </c>
+      <c r="C6" t="str">
+        <v>冲突修复</v>
+      </c>
+      <c r="D6" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E6" t="str">
+        <v>script</v>
+      </c>
+      <c r="F6" t="str">
+        <v>all</v>
+      </c>
+      <c r="G6" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H6" t="str">
+        <v>学生冲突反复发生且难以修复</v>
+      </c>
+      <c r="I6" t="str">
+        <v>high</v>
+      </c>
+      <c r="J6" t="str">
+        <v>CS_AT_RELATION</v>
+      </c>
+      <c r="K6" t="str">
+        <v>关系系统受损</v>
+      </c>
+      <c r="L6" t="str">
+        <v>class_system,relation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>CS_RELATION</v>
+      </c>
+      <c r="N6" t="str">
+        <v>建立可重复的冲突处理流程</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">分开双方，各自说清「发生了什么」，只说事实
+各自说「我当时的感受」，不评价对方
+各自说「我希望接下来怎样」
+共同确认一个可执行的下一步，并约定检查时间</v>
+      </c>
+      <c r="P6" t="str">
+        <v>我们先不讨论谁对谁错，先把事实说清楚。</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>同类冲突复发率下降</v>
+      </c>
+      <c r="R6" t="str">
+        <v>20 分钟</v>
+      </c>
+      <c r="S6" t="str">
+        <v>按需</v>
+      </c>
+      <c r="T6" t="str">
+        <v>30</v>
+      </c>
+      <c r="U6" t="str">
+        <v>不要在全班面前处理个体冲突</v>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>修复式实践在班级管理中的应用</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>双方均能说出对方的诉求</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>任一方拒绝进入流程</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AI6" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>CS_RX_006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>同伴互助配对表</v>
+      </c>
+      <c r="C7" t="str">
+        <v>互助配对</v>
+      </c>
+      <c r="D7" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E7" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F7" t="str">
+        <v>all</v>
+      </c>
+      <c r="G7" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H7" t="str">
+        <v>班级缺少稳定的同伴支持结构</v>
+      </c>
+      <c r="I7" t="str">
+        <v>low</v>
+      </c>
+      <c r="J7" t="str">
+        <v>CS_AT_RELATION</v>
+      </c>
+      <c r="K7" t="str">
+        <v>关系系统受损</v>
+      </c>
+      <c r="L7" t="str">
+        <v>class_system,relation</v>
+      </c>
+      <c r="M7" t="str">
+        <v>CS_RELATION</v>
+      </c>
+      <c r="N7" t="str">
+        <v>建立可持续的同伴互助关系</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">按学习和性格互补原则做两两配对
+给每对一个具体的互助任务，如每天互查作业
+每周收一次简短反馈，只问「这周互相帮到了什么」
+两周后按反馈调整配对</v>
+      </c>
+      <c r="P7" t="str">
+        <v>你们两个这周互相提醒一下，周五我来听听你们互相帮到了什么。</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>被孤立学生数量下降</v>
+      </c>
+      <c r="R7" t="str">
+        <v>20 分钟</v>
+      </c>
+      <c r="S7" t="str">
+        <v>每月调整一次</v>
+      </c>
+      <c r="T7" t="str">
+        <v>30</v>
+      </c>
+      <c r="U7" t="str">
+        <v>不要把配对当成优生帮差生的单向安排</v>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>C</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>同伴支持机制实务</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>80% 配对能说出互助内容</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>半数配对无实际互动</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -966,95 +1234,95 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C_RX_001</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>离开当前情境</v>
+        <v>和学生一起用一句话说清本</v>
       </c>
       <c r="D2" t="str">
-        <v>暂时离开当前工作环境（办公室、教室），找到一个安静不被打扰的空间</v>
+        <v>和学生一起用一句话说清本学期班级要成为什么样</v>
       </c>
       <c r="E2" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>不需要走很远，去走廊尽头或空会议室即可</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>我们这学期只做好一件事，你们觉得应该是哪一件？</v>
       </c>
       <c r="I2" t="str">
-        <v>教师已经离开原环境，至少获得3分钟不被干扰的时间</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J2" t="str">
-        <v>如果实在无法离开怎么办？（答：至少转身背对工作区域，闭眼30秒）</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C_RX_001</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>三轮缓慢呼吸</v>
+        <v>把这句话拆成三个可观察的</v>
       </c>
       <c r="D3" t="str">
-        <v>进行三轮缓慢深呼吸：吸气4秒→屏息2秒→呼气6秒。每轮之间自然呼吸10秒</v>
+        <v>把这句话拆成三个可观察的里程碑</v>
       </c>
       <c r="E3" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>计时器（可选）</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>不要刻意用力呼吸，重点是让呼气比吸气更长</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>完成了三轮呼吸</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J3" t="str">
-        <v>如果注意力无法集中怎么办？（答：把注意力放在呼气的感觉上，每次走神都重新回来即可）</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>C_RX_001</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>命名此刻的情绪</v>
+        <v>为第一个里程碑写清完成标</v>
       </c>
       <c r="D4" t="str">
-        <v>问自己「我现在感受到的是什么？」——是愤怒、委屈、无力、焦虑、还是别的？给情绪一个名字</v>
+        <v>为第一个里程碑写清完成标准和检查时间</v>
       </c>
       <c r="E4" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>不需要分析原因，只需要命名。如果同时有多种情绪，选最强烈的那一个</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>教师能够说出至少一种情绪的名称</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1062,31 +1330,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>C_RX_001</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>选一个最小行动</v>
+        <v>贴在教室并每两周对照一次</v>
       </c>
       <c r="D5" t="str">
-        <v>问自己「接下来5分钟，我能做的最小、最简单的一件事是什么？」选一件，然后做</v>
+        <v>贴在教室并每两周对照一次</v>
       </c>
       <c r="E5" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>最小行动的标准：不需要别人配合，不需要准备，立即能做</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>教师选出了至少一个可行的最小行动</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1094,31 +1362,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>C_RX_002</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>记录今日能量</v>
+        <v>选一个每天都发生的事务（</v>
       </c>
       <c r="D6" t="str">
-        <v>在能量记录卡上记录你今天几个关键时间点的能量状态（1-10分）</v>
+        <v>选一个每天都发生的事务（如晨检、放学清扫）</v>
       </c>
       <c r="E6" t="str">
-        <v>3分钟</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>能量记录卡</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>保持诚实，不需要美化</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>这件事从明天起由你负责，遇到处理不了的情况再来找我。</v>
       </c>
       <c r="I6" t="str">
-        <v>完成了至少3个时间点的记录</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1126,46 +1394,622 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>C_RX_002</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>识别能量消耗</v>
+        <v>写清责任人、执行步骤、异</v>
       </c>
       <c r="D7" t="str">
-        <v>回顾今天的能量低谷，思考是什么消耗了你的能量</v>
+        <v>写清责任人、执行步骤、异常处理和复盘时间</v>
       </c>
       <c r="E7" t="str">
-        <v>2分钟</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>不需要找出所有原因，选影响最大的1-2个即可</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>识别出至少1个能量消耗源</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CS_RX_002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>让学生试运行三天，教师只</v>
+      </c>
+      <c r="D8" t="str">
+        <v>让学生试运行三天，教师只观察不介入</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_RX_002</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" t="str">
+        <v>第四天复盘，只调整卡住的</v>
+      </c>
+      <c r="D9" t="str">
+        <v>第四天复盘，只调整卡住的那一步</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_RX_003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>活动结束当天，留出十分钟</v>
+      </c>
+      <c r="D10" t="str">
+        <v>活动结束当天，留出十分钟</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H10" t="str">
+        <v>今天我们只讨论一件事：哪个环节帮助大家更稳定，哪个环节明天需要调整。</v>
+      </c>
+      <c r="I10" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_RX_003</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>每人说一个「下次要保留的</v>
+      </c>
+      <c r="D11" t="str">
+        <v>每人说一个「下次要保留的动作」</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_RX_003</v>
+      </c>
+      <c r="B12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>每人说一个「下次要调整的</v>
+      </c>
+      <c r="D12" t="str">
+        <v>每人说一个「下次要调整的动作」</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_RX_003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>教师只记录不评价，把结果</v>
+      </c>
+      <c r="D13" t="str">
+        <v>教师只记录不评价，把结果贴在班级角</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_RX_004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>挑一条最常被违反的规则</v>
+      </c>
+      <c r="D14" t="str">
+        <v>挑一条最常被违反的规则</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H14" t="str">
+        <v>这条规则不是为了限制大家，而是为了让学习和相处更可预期。我们先试行三天再复盘。</v>
+      </c>
+      <c r="I14" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_RX_004</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>让学生说出这条规则存在的</v>
+      </c>
+      <c r="D15" t="str">
+        <v>让学生说出这条规则存在的理由，教师补充缺失的部分</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_RX_004</v>
+      </c>
+      <c r="B16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>一起把规则改写成可观察的</v>
+      </c>
+      <c r="D16" t="str">
+        <v>一起把规则改写成可观察的行为描述</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_RX_004</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17" t="str">
+        <v>约定试行两周后复盘</v>
+      </c>
+      <c r="D17" t="str">
+        <v>约定试行两周后复盘</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_RX_005</v>
+      </c>
+      <c r="B18" t="str">
+        <v>1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>分开双方，各自说清「发生</v>
+      </c>
+      <c r="D18" t="str">
+        <v>分开双方，各自说清「发生了什么」，只说事实</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H18" t="str">
+        <v>我们先不讨论谁对谁错，先把事实说清楚。</v>
+      </c>
+      <c r="I18" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_RX_005</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>各自说「我当时的感受」，</v>
+      </c>
+      <c r="D19" t="str">
+        <v>各自说「我当时的感受」，不评价对方</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CS_RX_005</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>各自说「我希望接下来怎样</v>
+      </c>
+      <c r="D20" t="str">
+        <v>各自说「我希望接下来怎样」</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CS_RX_005</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4</v>
+      </c>
+      <c r="C21" t="str">
+        <v>共同确认一个可执行的下一</v>
+      </c>
+      <c r="D21" t="str">
+        <v>共同确认一个可执行的下一步，并约定检查时间</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CS_RX_006</v>
+      </c>
+      <c r="B22" t="str">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>按学习和性格互补原则做两</v>
+      </c>
+      <c r="D22" t="str">
+        <v>按学习和性格互补原则做两两配对</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H22" t="str">
+        <v>你们两个这周互相提醒一下，周五我来听听你们互相帮到了什么。</v>
+      </c>
+      <c r="I22" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_RX_006</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>给每对一个具体的互助任务</v>
+      </c>
+      <c r="D23" t="str">
+        <v>给每对一个具体的互助任务，如每天互查作业</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_RX_006</v>
+      </c>
+      <c r="B24" t="str">
+        <v>3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>每周收一次简短反馈，只问</v>
+      </c>
+      <c r="D24" t="str">
+        <v>每周收一次简短反馈，只问「这周互相帮到了什么」</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_RX_006</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>两周后按反馈调整配对</v>
+      </c>
+      <c r="D25" t="str">
+        <v>两周后按反馈调整配对</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1192,76 +2036,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C_RX_001</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="B2" t="str">
-        <v>教师自评抑郁量表得分&gt;=15</v>
+        <v>冲突涉及肢体伤害或欺凌</v>
       </c>
       <c r="C2" t="str">
         <v>block</v>
       </c>
       <c r="D2" t="str">
-        <v>抑郁风险较高时应先进行专业心理评估，不可单独依赖呼吸练习</v>
+        <v>涉及安全事件须优先启动应急流程而非同伴调解</v>
       </c>
       <c r="E2" t="str">
-        <v>通知心理专员进行评估</v>
+        <v>启动校园安全应急预案并通知年级组长</v>
       </c>
       <c r="F2" t="str">
-        <v>存在抑郁风险的教师</v>
+        <v>班主任</v>
       </c>
       <c r="G2" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>C_RX_004</v>
-      </c>
-      <c r="B3" t="str">
-        <v>教师处于急性危机状态</v>
-      </c>
-      <c r="C3" t="str">
-        <v>block</v>
-      </c>
-      <c r="D3" t="str">
-        <v>急性危机时认知重构类工具可能加重混乱感</v>
-      </c>
-      <c r="E3" t="str">
-        <v>先使用安全稳定化工具，等状态稳定后再使用</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>C_RX_003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>参与教师超过8人</v>
-      </c>
-      <c r="C4" t="str">
-        <v>warn</v>
-      </c>
-      <c r="D4" t="str">
-        <v>超过8人时小组讨论深度下降，建议拆分小组</v>
-      </c>
-      <c r="E4" t="str">
-        <v>每组控制在4-6人，增加一名引导员</v>
-      </c>
-      <c r="F4" t="str">
-        <v>年级组长</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>班级系统建设手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/tool.xlsx
+++ b/business-libraries/test-data/class_system/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>CS_RX_001</v>
+        <v>CS_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>班级目标里程碑拆解表</v>
       </c>
       <c r="C2" t="str">
-        <v>目标拆解</v>
+        <v>班级目标里程碑拆</v>
       </c>
       <c r="D2" t="str">
         <v>class_system</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>CS_AT_GOAL</v>
+        <v>CS_AT_01</v>
       </c>
       <c r="K2" t="str">
         <v>目标系统未落地</v>
@@ -549,16 +549,13 @@
         <v>class_system,goal</v>
       </c>
       <c r="M2" t="str">
-        <v>CS_GOAL</v>
+        <v>CS_S1D1</v>
       </c>
       <c r="N2" t="str">
         <v>把抽象目标转成可观察的阶段成果</v>
       </c>
-      <c r="O2" t="str" xml:space="preserve">
-        <v xml:space="preserve">和学生一起用一句话说清本学期班级要成为什么样
-把这句话拆成三个可观察的里程碑
-为第一个里程碑写清完成标准和检查时间
-贴在教室并每两周对照一次</v>
+      <c r="O2" t="str">
+        <v>和学生一起用一句话说清本学期班级要成为什么样；把这句话拆成三个可观察的里程碑；为第一个里程碑写清完成标准和检查时间；贴在教室并每两周对照一次</v>
       </c>
       <c r="P2" t="str">
         <v>我们这学期只做好一件事，你们觉得应该是哪一件？</v>
@@ -618,21 +615,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>CS_RX_002</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="B3" t="str">
         <v>班级事务 SOP 卡</v>
       </c>
       <c r="C3" t="str">
-        <v>事务SOP</v>
+        <v>班级事务 SOP</v>
       </c>
       <c r="D3" t="str">
         <v>class_system</v>
@@ -653,25 +650,22 @@
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="K3" t="str">
-        <v>组织系统缺位</v>
+        <v>权力系统缺位</v>
       </c>
       <c r="L3" t="str">
         <v>class_system,org</v>
       </c>
       <c r="M3" t="str">
-        <v>CS_ORG</v>
+        <v>CS_S1D2</v>
       </c>
       <c r="N3" t="str">
         <v>把日常事务转成学生可独立执行的流程</v>
       </c>
-      <c r="O3" t="str" xml:space="preserve">
-        <v xml:space="preserve">选一个每天都发生的事务（如晨检、放学清扫）
-写清责任人、执行步骤、异常处理和复盘时间
-让学生试运行三天，教师只观察不介入
-第四天复盘，只调整卡住的那一步</v>
+      <c r="O3" t="str">
+        <v>选一个每天都发生的事务（如晨检、放学清扫）；写清责任人、执行步骤、异常处理和复盘时间；让学生试运行三天，教师只观察不介入；第四天复盘，只调整卡住的那一步</v>
       </c>
       <c r="P3" t="str">
         <v>这件事从明天起由你负责，遇到处理不了的情况再来找我。</v>
@@ -731,21 +725,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>CS_RX_003</v>
+        <v>CS_RX_03</v>
       </c>
       <c r="B4" t="str">
         <v>十分钟班级微复盘</v>
       </c>
       <c r="C4" t="str">
-        <v>微复盘</v>
+        <v>十分钟班级微复盘</v>
       </c>
       <c r="D4" t="str">
         <v>class_system</v>
@@ -766,25 +760,22 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03;CS_AT_06</v>
       </c>
       <c r="K4" t="str">
-        <v>活动系统空转</v>
+        <v>情感系统空转;堰塞湖蓄积风险</v>
       </c>
       <c r="L4" t="str">
-        <v>class_system,activity</v>
+        <v>class_system,activity,warning,dam</v>
       </c>
       <c r="M4" t="str">
-        <v>CS_ACTIVITY</v>
+        <v>CS_S1D3</v>
       </c>
       <c r="N4" t="str">
         <v>把活动经验转成可重复的改进</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
-        <v xml:space="preserve">活动结束当天，留出十分钟
-每人说一个「下次要保留的动作」
-每人说一个「下次要调整的动作」
-教师只记录不评价，把结果贴在班级角</v>
+      <c r="O4" t="str">
+        <v>活动结束当天，留出十分钟；每人说一个「下次要保留的动作」；每人说一个「下次要调整的动作」；教师只记录不评价，把结果贴在班级角</v>
       </c>
       <c r="P4" t="str">
         <v>今天我们只讨论一件事：哪个环节帮助大家更稳定，哪个环节明天需要调整。</v>
@@ -844,21 +835,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>CS_RX_004</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B5" t="str">
         <v>规则共构工作坊</v>
       </c>
       <c r="C5" t="str">
-        <v>规则共构</v>
+        <v>规则共构工作坊</v>
       </c>
       <c r="D5" t="str">
         <v>class_system</v>
@@ -879,25 +870,22 @@
         <v>medium</v>
       </c>
       <c r="J5" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04;CS_AT_06</v>
       </c>
       <c r="K5" t="str">
-        <v>环境系统薄弱</v>
+        <v>规范系统薄弱;堰塞湖蓄积风险</v>
       </c>
       <c r="L5" t="str">
-        <v>class_system,environment</v>
+        <v>class_system,environment,warning,dam</v>
       </c>
       <c r="M5" t="str">
-        <v>CS_ENV</v>
+        <v>CS_S1D4</v>
       </c>
       <c r="N5" t="str">
         <v>把规则从教师要求转成共同约定</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
-        <v xml:space="preserve">挑一条最常被违反的规则
-让学生说出这条规则存在的理由，教师补充缺失的部分
-一起把规则改写成可观察的行为描述
-约定试行两周后复盘</v>
+      <c r="O5" t="str">
+        <v>挑一条最常被违反的规则；让学生说出这条规则存在的理由，教师补充缺失的部分；一起把规则改写成可观察的行为描述；约定试行两周后复盘</v>
       </c>
       <c r="P5" t="str">
         <v>这条规则不是为了限制大家，而是为了让学习和相处更可预期。我们先试行三天再复盘。</v>
@@ -957,21 +945,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6" t="str">
-        <v>CS_RX_005</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B6" t="str">
         <v>冲突修复四步法</v>
       </c>
       <c r="C6" t="str">
-        <v>冲突修复</v>
+        <v>冲突修复四步法</v>
       </c>
       <c r="D6" t="str">
         <v>class_system</v>
@@ -992,25 +980,22 @@
         <v>high</v>
       </c>
       <c r="J6" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05;CS_AT_06</v>
       </c>
       <c r="K6" t="str">
-        <v>关系系统受损</v>
+        <v>关系系统受损;堰塞湖蓄积风险</v>
       </c>
       <c r="L6" t="str">
-        <v>class_system,relation</v>
+        <v>class_system,relation,warning,dam</v>
       </c>
       <c r="M6" t="str">
-        <v>CS_RELATION</v>
+        <v>CS_S1D5</v>
       </c>
       <c r="N6" t="str">
         <v>建立可重复的冲突处理流程</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">分开双方，各自说清「发生了什么」，只说事实
-各自说「我当时的感受」，不评价对方
-各自说「我希望接下来怎样」
-共同确认一个可执行的下一步，并约定检查时间</v>
+      <c r="O6" t="str">
+        <v>分开双方，各自说清「发生了什么」，只说事实；各自说「我当时的感受」，不评价对方；各自说「我希望接下来怎样」；共同确认一个可执行的下一步，并约定检查时间</v>
       </c>
       <c r="P6" t="str">
         <v>我们先不讨论谁对谁错，先把事实说清楚。</v>
@@ -1070,21 +1055,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
-        <v>CS_RX_006</v>
+        <v>CS_RX_06</v>
       </c>
       <c r="B7" t="str">
         <v>同伴互助配对表</v>
       </c>
       <c r="C7" t="str">
-        <v>互助配对</v>
+        <v>同伴互助配对表</v>
       </c>
       <c r="D7" t="str">
         <v>class_system</v>
@@ -1105,7 +1090,7 @@
         <v>low</v>
       </c>
       <c r="J7" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="K7" t="str">
         <v>关系系统受损</v>
@@ -1114,16 +1099,13 @@
         <v>class_system,relation</v>
       </c>
       <c r="M7" t="str">
-        <v>CS_RELATION</v>
+        <v>CS_S1D5</v>
       </c>
       <c r="N7" t="str">
         <v>建立可持续的同伴互助关系</v>
       </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">按学习和性格互补原则做两两配对
-给每对一个具体的互助任务，如每天互查作业
-每周收一次简短反馈，只问「这周互相帮到了什么」
-两周后按反馈调整配对</v>
+      <c r="O7" t="str">
+        <v>按学习和性格互补原则做两两配对；给每对一个具体的互助任务，如每天互查作业；每周收一次简短反馈，只问「这周互相帮到了什么」；两周后按反馈调整配对</v>
       </c>
       <c r="P7" t="str">
         <v>你们两个这周互相提醒一下，周五我来听听你们互相帮到了什么。</v>
@@ -1183,7 +1165,7 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
@@ -1234,13 +1216,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_RX_001</v>
+        <v>CS_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>和学生一起用一句话说清本</v>
+        <v>和学生一起用一句话说清本学期班级要成为什么样</v>
       </c>
       <c r="D2" t="str">
         <v>和学生一起用一句话说清本学期班级要成为什么样</v>
@@ -1266,13 +1248,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_RX_001</v>
+        <v>CS_RX_01</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>把这句话拆成三个可观察的</v>
+        <v>把这句话拆成三个可观察的里程碑</v>
       </c>
       <c r="D3" t="str">
         <v>把这句话拆成三个可观察的里程碑</v>
@@ -1298,13 +1280,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_RX_001</v>
+        <v>CS_RX_01</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>为第一个里程碑写清完成标</v>
+        <v>为第一个里程碑写清完成标准和检查时间</v>
       </c>
       <c r="D4" t="str">
         <v>为第一个里程碑写清完成标准和检查时间</v>
@@ -1330,7 +1312,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_RX_001</v>
+        <v>CS_RX_01</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
@@ -1362,13 +1344,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_RX_002</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>选一个每天都发生的事务（</v>
+        <v>选一个每天都发生的事务（如晨检、放学清扫）</v>
       </c>
       <c r="D6" t="str">
         <v>选一个每天都发生的事务（如晨检、放学清扫）</v>
@@ -1394,13 +1376,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_RX_002</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>写清责任人、执行步骤、异</v>
+        <v>写清责任人、执行步骤、异常处理和复盘时间</v>
       </c>
       <c r="D7" t="str">
         <v>写清责任人、执行步骤、异常处理和复盘时间</v>
@@ -1426,13 +1408,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_RX_002</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>让学生试运行三天，教师只</v>
+        <v>让学生试运行三天，教师只观察不介入</v>
       </c>
       <c r="D8" t="str">
         <v>让学生试运行三天，教师只观察不介入</v>
@@ -1458,13 +1440,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CS_RX_002</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>第四天复盘，只调整卡住的</v>
+        <v>第四天复盘，只调整卡住的那一步</v>
       </c>
       <c r="D9" t="str">
         <v>第四天复盘，只调整卡住的那一步</v>
@@ -1490,7 +1472,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CS_RX_003</v>
+        <v>CS_RX_03</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
@@ -1522,13 +1504,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CS_RX_003</v>
+        <v>CS_RX_03</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>每人说一个「下次要保留的</v>
+        <v>每人说一个「下次要保留的动作」</v>
       </c>
       <c r="D11" t="str">
         <v>每人说一个「下次要保留的动作」</v>
@@ -1554,13 +1536,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_RX_003</v>
+        <v>CS_RX_03</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>每人说一个「下次要调整的</v>
+        <v>每人说一个「下次要调整的动作」</v>
       </c>
       <c r="D12" t="str">
         <v>每人说一个「下次要调整的动作」</v>
@@ -1586,13 +1568,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CS_RX_003</v>
+        <v>CS_RX_03</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>教师只记录不评价，把结果</v>
+        <v>教师只记录不评价，把结果贴在班级角</v>
       </c>
       <c r="D13" t="str">
         <v>教师只记录不评价，把结果贴在班级角</v>
@@ -1618,7 +1600,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_RX_004</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
@@ -1650,13 +1632,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_RX_004</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>让学生说出这条规则存在的</v>
+        <v>让学生说出这条规则存在的理由，教师补充缺失的部分</v>
       </c>
       <c r="D15" t="str">
         <v>让学生说出这条规则存在的理由，教师补充缺失的部分</v>
@@ -1682,13 +1664,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CS_RX_004</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>一起把规则改写成可观察的</v>
+        <v>一起把规则改写成可观察的行为描述</v>
       </c>
       <c r="D16" t="str">
         <v>一起把规则改写成可观察的行为描述</v>
@@ -1714,7 +1696,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CS_RX_004</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
@@ -1746,13 +1728,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CS_RX_005</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>分开双方，各自说清「发生</v>
+        <v>分开双方，各自说清「发生了什么」，只说事实</v>
       </c>
       <c r="D18" t="str">
         <v>分开双方，各自说清「发生了什么」，只说事实</v>
@@ -1778,13 +1760,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CS_RX_005</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>各自说「我当时的感受」，</v>
+        <v>各自说「我当时的感受」，不评价对方</v>
       </c>
       <c r="D19" t="str">
         <v>各自说「我当时的感受」，不评价对方</v>
@@ -1810,13 +1792,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CS_RX_005</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>各自说「我希望接下来怎样</v>
+        <v>各自说「我希望接下来怎样」</v>
       </c>
       <c r="D20" t="str">
         <v>各自说「我希望接下来怎样」</v>
@@ -1842,13 +1824,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CS_RX_005</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>共同确认一个可执行的下一</v>
+        <v>共同确认一个可执行的下一步，并约定检查时间</v>
       </c>
       <c r="D21" t="str">
         <v>共同确认一个可执行的下一步，并约定检查时间</v>
@@ -1874,13 +1856,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CS_RX_006</v>
+        <v>CS_RX_06</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>按学习和性格互补原则做两</v>
+        <v>按学习和性格互补原则做两两配对</v>
       </c>
       <c r="D22" t="str">
         <v>按学习和性格互补原则做两两配对</v>
@@ -1906,13 +1888,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CS_RX_006</v>
+        <v>CS_RX_06</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>给每对一个具体的互助任务</v>
+        <v>给每对一个具体的互助任务，如每天互查作业</v>
       </c>
       <c r="D23" t="str">
         <v>给每对一个具体的互助任务，如每天互查作业</v>
@@ -1938,13 +1920,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CS_RX_006</v>
+        <v>CS_RX_06</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>每周收一次简短反馈，只问</v>
+        <v>每周收一次简短反馈，只问「这周互相帮到了什么」</v>
       </c>
       <c r="D24" t="str">
         <v>每周收一次简短反馈，只问「这周互相帮到了什么」</v>
@@ -1970,7 +1952,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CS_RX_006</v>
+        <v>CS_RX_06</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
@@ -2036,7 +2018,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_RX_005</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B2" t="str">
         <v>冲突涉及肢体伤害或欺凌</v>

--- a/business-libraries/test-data/class_system/tool.xlsx
+++ b/business-libraries/test-data/class_system/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>CS_RX_01</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>班级目标里程碑拆解表</v>
       </c>
       <c r="C2" t="str">
-        <v>班级目标里程碑拆</v>
+        <v>目标拆解</v>
       </c>
       <c r="D2" t="str">
         <v>class_system</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>CS_AT_01</v>
+        <v>CS_AT_GOAL</v>
       </c>
       <c r="K2" t="str">
         <v>目标系统未落地</v>
@@ -549,13 +549,16 @@
         <v>class_system,goal</v>
       </c>
       <c r="M2" t="str">
-        <v>CS_S1D1</v>
+        <v>CS_GOAL</v>
       </c>
       <c r="N2" t="str">
         <v>把抽象目标转成可观察的阶段成果</v>
       </c>
-      <c r="O2" t="str">
-        <v>和学生一起用一句话说清本学期班级要成为什么样；把这句话拆成三个可观察的里程碑；为第一个里程碑写清完成标准和检查时间；贴在教室并每两周对照一次</v>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">和学生一起用一句话说清本学期班级要成为什么样
+把这句话拆成三个可观察的里程碑
+为第一个里程碑写清完成标准和检查时间
+贴在教室并每两周对照一次</v>
       </c>
       <c r="P2" t="str">
         <v>我们这学期只做好一件事，你们觉得应该是哪一件？</v>
@@ -615,21 +618,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>CS_RX_02</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B3" t="str">
         <v>班级事务 SOP 卡</v>
       </c>
       <c r="C3" t="str">
-        <v>班级事务 SOP</v>
+        <v>事务SOP</v>
       </c>
       <c r="D3" t="str">
         <v>class_system</v>
@@ -650,22 +653,25 @@
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>CS_AT_02</v>
+        <v>CS_AT_ORG</v>
       </c>
       <c r="K3" t="str">
-        <v>权力系统缺位</v>
+        <v>组织系统缺位</v>
       </c>
       <c r="L3" t="str">
         <v>class_system,org</v>
       </c>
       <c r="M3" t="str">
-        <v>CS_S1D2</v>
+        <v>CS_ORG</v>
       </c>
       <c r="N3" t="str">
         <v>把日常事务转成学生可独立执行的流程</v>
       </c>
-      <c r="O3" t="str">
-        <v>选一个每天都发生的事务（如晨检、放学清扫）；写清责任人、执行步骤、异常处理和复盘时间；让学生试运行三天，教师只观察不介入；第四天复盘，只调整卡住的那一步</v>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">选一个每天都发生的事务（如晨检、放学清扫）
+写清责任人、执行步骤、异常处理和复盘时间
+让学生试运行三天，教师只观察不介入
+第四天复盘，只调整卡住的那一步</v>
       </c>
       <c r="P3" t="str">
         <v>这件事从明天起由你负责，遇到处理不了的情况再来找我。</v>
@@ -725,21 +731,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>CS_RX_03</v>
+        <v>CS_RX_003</v>
       </c>
       <c r="B4" t="str">
         <v>十分钟班级微复盘</v>
       </c>
       <c r="C4" t="str">
-        <v>十分钟班级微复盘</v>
+        <v>微复盘</v>
       </c>
       <c r="D4" t="str">
         <v>class_system</v>
@@ -760,22 +766,25 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>CS_AT_03;CS_AT_06</v>
+        <v>CS_AT_ACTIVITY</v>
       </c>
       <c r="K4" t="str">
-        <v>情感系统空转;堰塞湖蓄积风险</v>
+        <v>活动系统空转</v>
       </c>
       <c r="L4" t="str">
-        <v>class_system,activity,warning,dam</v>
+        <v>class_system,activity</v>
       </c>
       <c r="M4" t="str">
-        <v>CS_S1D3</v>
+        <v>CS_ACTIVITY</v>
       </c>
       <c r="N4" t="str">
         <v>把活动经验转成可重复的改进</v>
       </c>
-      <c r="O4" t="str">
-        <v>活动结束当天，留出十分钟；每人说一个「下次要保留的动作」；每人说一个「下次要调整的动作」；教师只记录不评价，把结果贴在班级角</v>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">活动结束当天，留出十分钟
+每人说一个「下次要保留的动作」
+每人说一个「下次要调整的动作」
+教师只记录不评价，把结果贴在班级角</v>
       </c>
       <c r="P4" t="str">
         <v>今天我们只讨论一件事：哪个环节帮助大家更稳定，哪个环节明天需要调整。</v>
@@ -835,21 +844,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="B5" t="str">
         <v>规则共构工作坊</v>
       </c>
       <c r="C5" t="str">
-        <v>规则共构工作坊</v>
+        <v>规则共构</v>
       </c>
       <c r="D5" t="str">
         <v>class_system</v>
@@ -870,22 +879,25 @@
         <v>medium</v>
       </c>
       <c r="J5" t="str">
-        <v>CS_AT_04;CS_AT_06</v>
+        <v>CS_AT_ENV</v>
       </c>
       <c r="K5" t="str">
-        <v>规范系统薄弱;堰塞湖蓄积风险</v>
+        <v>环境系统薄弱</v>
       </c>
       <c r="L5" t="str">
-        <v>class_system,environment,warning,dam</v>
+        <v>class_system,environment</v>
       </c>
       <c r="M5" t="str">
-        <v>CS_S1D4</v>
+        <v>CS_ENV</v>
       </c>
       <c r="N5" t="str">
         <v>把规则从教师要求转成共同约定</v>
       </c>
-      <c r="O5" t="str">
-        <v>挑一条最常被违反的规则；让学生说出这条规则存在的理由，教师补充缺失的部分；一起把规则改写成可观察的行为描述；约定试行两周后复盘</v>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">挑一条最常被违反的规则
+让学生说出这条规则存在的理由，教师补充缺失的部分
+一起把规则改写成可观察的行为描述
+约定试行两周后复盘</v>
       </c>
       <c r="P5" t="str">
         <v>这条规则不是为了限制大家，而是为了让学习和相处更可预期。我们先试行三天再复盘。</v>
@@ -945,21 +957,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="B6" t="str">
         <v>冲突修复四步法</v>
       </c>
       <c r="C6" t="str">
-        <v>冲突修复四步法</v>
+        <v>冲突修复</v>
       </c>
       <c r="D6" t="str">
         <v>class_system</v>
@@ -980,22 +992,25 @@
         <v>high</v>
       </c>
       <c r="J6" t="str">
-        <v>CS_AT_05;CS_AT_06</v>
+        <v>CS_AT_RELATION</v>
       </c>
       <c r="K6" t="str">
-        <v>关系系统受损;堰塞湖蓄积风险</v>
+        <v>关系系统受损</v>
       </c>
       <c r="L6" t="str">
-        <v>class_system,relation,warning,dam</v>
+        <v>class_system,relation</v>
       </c>
       <c r="M6" t="str">
-        <v>CS_S1D5</v>
+        <v>CS_RELATION</v>
       </c>
       <c r="N6" t="str">
         <v>建立可重复的冲突处理流程</v>
       </c>
-      <c r="O6" t="str">
-        <v>分开双方，各自说清「发生了什么」，只说事实；各自说「我当时的感受」，不评价对方；各自说「我希望接下来怎样」；共同确认一个可执行的下一步，并约定检查时间</v>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">分开双方，各自说清「发生了什么」，只说事实
+各自说「我当时的感受」，不评价对方
+各自说「我希望接下来怎样」
+共同确认一个可执行的下一步，并约定检查时间</v>
       </c>
       <c r="P6" t="str">
         <v>我们先不讨论谁对谁错，先把事实说清楚。</v>
@@ -1055,21 +1070,21 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_006</v>
       </c>
       <c r="B7" t="str">
         <v>同伴互助配对表</v>
       </c>
       <c r="C7" t="str">
-        <v>同伴互助配对表</v>
+        <v>互助配对</v>
       </c>
       <c r="D7" t="str">
         <v>class_system</v>
@@ -1090,7 +1105,7 @@
         <v>low</v>
       </c>
       <c r="J7" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_RELATION</v>
       </c>
       <c r="K7" t="str">
         <v>关系系统受损</v>
@@ -1099,13 +1114,16 @@
         <v>class_system,relation</v>
       </c>
       <c r="M7" t="str">
-        <v>CS_S1D5</v>
+        <v>CS_RELATION</v>
       </c>
       <c r="N7" t="str">
         <v>建立可持续的同伴互助关系</v>
       </c>
-      <c r="O7" t="str">
-        <v>按学习和性格互补原则做两两配对；给每对一个具体的互助任务，如每天互查作业；每周收一次简短反馈，只问「这周互相帮到了什么」；两周后按反馈调整配对</v>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">按学习和性格互补原则做两两配对
+给每对一个具体的互助任务，如每天互查作业
+每周收一次简短反馈，只问「这周互相帮到了什么」
+两周后按反馈调整配对</v>
       </c>
       <c r="P7" t="str">
         <v>你们两个这周互相提醒一下，周五我来听听你们互相帮到了什么。</v>
@@ -1165,7 +1183,7 @@
         <v>班级系统建设手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
@@ -1216,13 +1234,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_RX_01</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>和学生一起用一句话说清本学期班级要成为什么样</v>
+        <v>和学生一起用一句话说清本</v>
       </c>
       <c r="D2" t="str">
         <v>和学生一起用一句话说清本学期班级要成为什么样</v>
@@ -1248,13 +1266,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_RX_01</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>把这句话拆成三个可观察的里程碑</v>
+        <v>把这句话拆成三个可观察的</v>
       </c>
       <c r="D3" t="str">
         <v>把这句话拆成三个可观察的里程碑</v>
@@ -1280,13 +1298,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_RX_01</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>为第一个里程碑写清完成标准和检查时间</v>
+        <v>为第一个里程碑写清完成标</v>
       </c>
       <c r="D4" t="str">
         <v>为第一个里程碑写清完成标准和检查时间</v>
@@ -1312,7 +1330,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_RX_01</v>
+        <v>CS_RX_001</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
@@ -1344,13 +1362,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_RX_02</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>选一个每天都发生的事务（如晨检、放学清扫）</v>
+        <v>选一个每天都发生的事务（</v>
       </c>
       <c r="D6" t="str">
         <v>选一个每天都发生的事务（如晨检、放学清扫）</v>
@@ -1376,13 +1394,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_RX_02</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>写清责任人、执行步骤、异常处理和复盘时间</v>
+        <v>写清责任人、执行步骤、异</v>
       </c>
       <c r="D7" t="str">
         <v>写清责任人、执行步骤、异常处理和复盘时间</v>
@@ -1408,13 +1426,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_RX_02</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>让学生试运行三天，教师只观察不介入</v>
+        <v>让学生试运行三天，教师只</v>
       </c>
       <c r="D8" t="str">
         <v>让学生试运行三天，教师只观察不介入</v>
@@ -1440,13 +1458,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CS_RX_02</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>第四天复盘，只调整卡住的那一步</v>
+        <v>第四天复盘，只调整卡住的</v>
       </c>
       <c r="D9" t="str">
         <v>第四天复盘，只调整卡住的那一步</v>
@@ -1472,7 +1490,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CS_RX_03</v>
+        <v>CS_RX_003</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
@@ -1504,13 +1522,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CS_RX_03</v>
+        <v>CS_RX_003</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>每人说一个「下次要保留的动作」</v>
+        <v>每人说一个「下次要保留的</v>
       </c>
       <c r="D11" t="str">
         <v>每人说一个「下次要保留的动作」</v>
@@ -1536,13 +1554,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_RX_03</v>
+        <v>CS_RX_003</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>每人说一个「下次要调整的动作」</v>
+        <v>每人说一个「下次要调整的</v>
       </c>
       <c r="D12" t="str">
         <v>每人说一个「下次要调整的动作」</v>
@@ -1568,13 +1586,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CS_RX_03</v>
+        <v>CS_RX_003</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>教师只记录不评价，把结果贴在班级角</v>
+        <v>教师只记录不评价，把结果</v>
       </c>
       <c r="D13" t="str">
         <v>教师只记录不评价，把结果贴在班级角</v>
@@ -1600,7 +1618,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
@@ -1632,13 +1650,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>让学生说出这条规则存在的理由，教师补充缺失的部分</v>
+        <v>让学生说出这条规则存在的</v>
       </c>
       <c r="D15" t="str">
         <v>让学生说出这条规则存在的理由，教师补充缺失的部分</v>
@@ -1664,13 +1682,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>一起把规则改写成可观察的行为描述</v>
+        <v>一起把规则改写成可观察的</v>
       </c>
       <c r="D16" t="str">
         <v>一起把规则改写成可观察的行为描述</v>
@@ -1696,7 +1714,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
@@ -1728,13 +1746,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>分开双方，各自说清「发生了什么」，只说事实</v>
+        <v>分开双方，各自说清「发生</v>
       </c>
       <c r="D18" t="str">
         <v>分开双方，各自说清「发生了什么」，只说事实</v>
@@ -1760,13 +1778,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>各自说「我当时的感受」，不评价对方</v>
+        <v>各自说「我当时的感受」，</v>
       </c>
       <c r="D19" t="str">
         <v>各自说「我当时的感受」，不评价对方</v>
@@ -1792,13 +1810,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>各自说「我希望接下来怎样」</v>
+        <v>各自说「我希望接下来怎样</v>
       </c>
       <c r="D20" t="str">
         <v>各自说「我希望接下来怎样」</v>
@@ -1824,13 +1842,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>共同确认一个可执行的下一步，并约定检查时间</v>
+        <v>共同确认一个可执行的下一</v>
       </c>
       <c r="D21" t="str">
         <v>共同确认一个可执行的下一步，并约定检查时间</v>
@@ -1856,13 +1874,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_006</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>按学习和性格互补原则做两两配对</v>
+        <v>按学习和性格互补原则做两</v>
       </c>
       <c r="D22" t="str">
         <v>按学习和性格互补原则做两两配对</v>
@@ -1888,13 +1906,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_006</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>给每对一个具体的互助任务，如每天互查作业</v>
+        <v>给每对一个具体的互助任务</v>
       </c>
       <c r="D23" t="str">
         <v>给每对一个具体的互助任务，如每天互查作业</v>
@@ -1920,13 +1938,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_006</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>每周收一次简短反馈，只问「这周互相帮到了什么」</v>
+        <v>每周收一次简短反馈，只问</v>
       </c>
       <c r="D24" t="str">
         <v>每周收一次简短反馈，只问「这周互相帮到了什么」</v>
@@ -1952,7 +1970,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_006</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
@@ -2018,7 +2036,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="B2" t="str">
         <v>冲突涉及肢体伤害或欺凌</v>

--- a/business-libraries/test-data/class_system/tool.xlsx
+++ b/business-libraries/test-data/class_system/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AJ32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -516,64 +516,64 @@
         <v>CS_RX_01</v>
       </c>
       <c r="B2" t="str">
-        <v>班级目标里程碑拆解表</v>
+        <v>五系统诊断向导</v>
       </c>
       <c r="C2" t="str">
-        <v>班级目标里程碑拆</v>
+        <v>五系统诊断向导</v>
       </c>
       <c r="D2" t="str">
         <v>class_system</v>
       </c>
       <c r="E2" t="str">
-        <v>worksheet</v>
+        <v>framework</v>
       </c>
       <c r="F2" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="G2" t="str">
         <v>teacher</v>
       </c>
       <c r="H2" t="str">
-        <v>学生说不出班级目标，或目标只停留在口号</v>
+        <v>学期初/中/末班级整体体检；定位短板系统</v>
       </c>
       <c r="I2" t="str">
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>CS_AT_01</v>
+        <v>CS_AT_01;CS_AT_02;CS_AT_03;CS_AT_04;CS_AT_05;CS_AT_06;CS_AT_07;CS_AT_08;CS_AT_09;CS_AT_10;CS_AT_11;CS_AT_12;CS_AT_13;CS_AT_14;CS_AT_15</v>
       </c>
       <c r="K2" t="str">
-        <v>目标系统未落地</v>
+        <v>亲师依恋断裂;同伴联结薄弱;家校连接松散;组织架构空缺;架构适配失当;运转机制失效;公约悬空;督导标准不一;危机响应迟滞;目标缺位;动力错配;学业堰塞;氛围负向;个体情绪失接;归属感缺失</v>
       </c>
       <c r="L2" t="str">
-        <v>class_system,goal</v>
+        <v>class_system,relationship,attachment,peer,family,organization,structure,seating,operation,norm,rules,supervision,crisis,goal,target,motivation,learning,emotion,climate,support,belonging</v>
       </c>
       <c r="M2" t="str">
-        <v>CS_S1D1</v>
+        <v>CS_S1D1;CS_S1D2;CS_S1D3;CS_S1D4;CS_S1D5</v>
       </c>
       <c r="N2" t="str">
-        <v>把抽象目标转成可观察的阶段成果</v>
+        <v>诊断→归因→匹配工具的总入口</v>
       </c>
       <c r="O2" t="str">
-        <v>和学生一起用一句话说清本学期班级要成为什么样；把这句话拆成三个可观察的里程碑；为第一个里程碑写清完成标准和检查时间；贴在教室并每两周对照一次</v>
+        <v>发放五系统自评表（15题，1-5分）；加总得15-75分；四档解读：60-75健康 / 45-59关注 / 30-44系统问题 / &lt;30立即介入；按短板系统匹配对应模块工具</v>
       </c>
       <c r="P2" t="str">
-        <v>我们这学期只做好一件事，你们觉得应该是哪一件？</v>
+        <v/>
       </c>
       <c r="Q2" t="str">
-        <v>学生能复述目标和第一个里程碑</v>
+        <v>定位最需要建设的班级子系统</v>
       </c>
       <c r="R2" t="str">
-        <v>一节班会</v>
+        <v>10 分钟</v>
       </c>
       <c r="S2" t="str">
-        <v>每学期一次</v>
+        <v>每学期初/中/末</v>
       </c>
       <c r="T2" t="str">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="U2" t="str">
-        <v>不要由教师单方面宣布目标</v>
+        <v>总分低于30时不要停留在常规建议，立即启动学校支援</v>
       </c>
       <c r="V2" t="str">
         <v/>
@@ -591,31 +591,31 @@
         <v>B</v>
       </c>
       <c r="AA2" t="str">
-        <v>班级系统建设手册 第2章</v>
+        <v>工作手册·第一章1.1</v>
       </c>
       <c r="AB2" t="str">
-        <v>随机抽问三名学生能说出目标</v>
+        <v>产出四档诊断结论并匹配短板工具</v>
       </c>
       <c r="AC2" t="str">
-        <v>两周后仍无人能复述</v>
+        <v>自评表回收率低或数据失真</v>
       </c>
       <c r="AD2" t="str">
-        <v>准备记录表</v>
+        <v>准备五系统自评表</v>
       </c>
       <c r="AE2" t="str">
-        <v>记录表</v>
+        <v>自评表（15题）、四档解读阈值</v>
       </c>
       <c r="AF2" t="str">
-        <v>一次执行记录</v>
+        <v>系统诊断结论</v>
       </c>
       <c r="AG2" t="str">
         <v/>
       </c>
       <c r="AH2" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AI2" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
@@ -626,64 +626,64 @@
         <v>CS_RX_02</v>
       </c>
       <c r="B3" t="str">
-        <v>班级事务 SOP 卡</v>
+        <v>堰塞湖破局法</v>
       </c>
       <c r="C3" t="str">
-        <v>班级事务 SOP</v>
+        <v>堰塞湖破局法</v>
       </c>
       <c r="D3" t="str">
         <v>class_system</v>
       </c>
       <c r="E3" t="str">
-        <v>checklist</v>
+        <v>framework</v>
       </c>
       <c r="F3" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="G3" t="str">
         <v>teacher</v>
       </c>
       <c r="H3" t="str">
-        <v>班级事务过度集中在教师身上</v>
+        <v>班级问题积累/突发（凝聚力骤降、班委集体辞职）</v>
       </c>
       <c r="I3" t="str">
         <v>high</v>
       </c>
       <c r="J3" t="str">
-        <v>CS_AT_02</v>
+        <v>CS_AT_12;CS_AT_13;CS_AT_14</v>
       </c>
       <c r="K3" t="str">
-        <v>权力系统缺位</v>
+        <v>学业堰塞;氛围负向;个体情绪失接</v>
       </c>
       <c r="L3" t="str">
-        <v>class_system,org</v>
+        <v>class_system,goal,learning,emotion,climate,support</v>
       </c>
       <c r="M3" t="str">
-        <v>CS_S1D2</v>
+        <v>CS_S1D5;CS_S1D4</v>
       </c>
       <c r="N3" t="str">
-        <v>把日常事务转成学生可独立执行的流程</v>
+        <v>把『为什么问题突然爆发』的水面下积累显性化并疏解</v>
       </c>
       <c r="O3" t="str">
-        <v>选一个每天都发生的事务（如晨检、放学清扫）；写清责任人、执行步骤、异常处理和复盘时间；让学生试运行三天，教师只观察不介入；第四天复盘，只调整卡住的那一步</v>
+        <v>识别4种截断（积累/堵塞/溃堤/重建）；疏浚SOP·定期排空：班会复盘；疏浚SOP·拓宽河道：声音通道；疏浚SOP·降低水位：小步成功；溃堤预警：出现集体辞职/安全事件立即启动危机响应</v>
       </c>
       <c r="P3" t="str">
-        <v>这件事从明天起由你负责，遇到处理不了的情况再来找我。</v>
+        <v/>
       </c>
       <c r="Q3" t="str">
-        <v>该事务连续一周无需教师介入</v>
+        <v>截断信号恢复表达，堰塞湖水位下降</v>
       </c>
       <c r="R3" t="str">
-        <v>30 分钟</v>
+        <v>一节班会</v>
       </c>
       <c r="S3" t="str">
-        <v>每两周新增一项</v>
+        <v>按需持续</v>
       </c>
       <c r="T3" t="str">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="U3" t="str">
-        <v>不要同时铺开多个 SOP；一次只做一项</v>
+        <v>出现集体辞职或安全事件时立即启动危机响应，不要按常规疏浚流程处理</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -701,31 +701,31 @@
         <v>B</v>
       </c>
       <c r="AA3" t="str">
-        <v>班级系统建设手册 第3章</v>
+        <v>工作手册·第一章1.3</v>
       </c>
       <c r="AB3" t="str">
-        <v>连续 5 天无需教师提醒</v>
+        <v>四类截断信号均有表达出口</v>
       </c>
       <c r="AC3" t="str">
-        <v>试运行三天内出现两次以上中断</v>
+        <v>出现集体辞职或安全事件</v>
       </c>
       <c r="AD3" t="str">
-        <v>准备记录表</v>
+        <v>准备截断识别卡</v>
       </c>
       <c r="AE3" t="str">
-        <v>记录表</v>
+        <v>堰塞湖模型、4种截断识别卡</v>
       </c>
       <c r="AF3" t="str">
-        <v>一次执行记录</v>
+        <v>疏浚行动计划</v>
       </c>
       <c r="AG3" t="str">
         <v/>
       </c>
       <c r="AH3" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AI3" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
@@ -736,10 +736,10 @@
         <v>CS_RX_03</v>
       </c>
       <c r="B4" t="str">
-        <v>十分钟班级微复盘</v>
+        <v>个案诊断矩阵应用</v>
       </c>
       <c r="C4" t="str">
-        <v>十分钟班级微复盘</v>
+        <v>个案诊断矩阵应用</v>
       </c>
       <c r="D4" t="str">
         <v>class_system</v>
@@ -748,52 +748,52 @@
         <v>framework</v>
       </c>
       <c r="F4" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="G4" t="str">
         <v>teacher</v>
       </c>
       <c r="H4" t="str">
-        <v>活动办完就结束，经验无法沉淀</v>
+        <v>单个学生问题行为归因与策略匹配</v>
       </c>
       <c r="I4" t="str">
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>CS_AT_03;CS_AT_06</v>
+        <v>CS_AT_11</v>
       </c>
       <c r="K4" t="str">
-        <v>情感系统空转;堰塞湖蓄积风险</v>
+        <v>动力错配</v>
       </c>
       <c r="L4" t="str">
-        <v>class_system,activity,warning,dam</v>
+        <v>class_system,goal,motivation</v>
       </c>
       <c r="M4" t="str">
-        <v>CS_S1D3</v>
+        <v>CS_S1D4</v>
       </c>
       <c r="N4" t="str">
-        <v>把活动经验转成可重复的改进</v>
+        <v>个案诊断（个体）区别于五系统（班级整体）诊断</v>
       </c>
       <c r="O4" t="str">
-        <v>活动结束当天，留出十分钟；每人说一个「下次要保留的动作」；每人说一个「下次要调整的动作」；教师只记录不评价，把结果贴在班级角</v>
+        <v>判能力（会不会）；判意愿（想不想）；定四型（成功/挫折/对抗/放弃）；匹配策略（赋能/拆解/连接/降门槛）</v>
       </c>
       <c r="P4" t="str">
-        <v>今天我们只讨论一件事：哪个环节帮助大家更稳定，哪个环节明天需要调整。</v>
+        <v/>
       </c>
       <c r="Q4" t="str">
-        <v>形成至少两条下次可执行的改进</v>
+        <v>个体行为问题归因清晰并匹配干预策略</v>
       </c>
       <c r="R4" t="str">
         <v>10 分钟</v>
       </c>
       <c r="S4" t="str">
-        <v>每次活动后</v>
+        <v>按需</v>
       </c>
       <c r="T4" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U4" t="str">
-        <v>教师不要在复盘中先发表意见</v>
+        <v>不用于替代危机处置</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -811,31 +811,31 @@
         <v>B</v>
       </c>
       <c r="AA4" t="str">
-        <v>班级系统建设手册 第4章</v>
+        <v>工作手册·第一章1.4</v>
       </c>
       <c r="AB4" t="str">
-        <v>产出 &gt;= 2 条具体改进</v>
+        <v>四型判定完成并给出策略</v>
       </c>
       <c r="AC4" t="str">
-        <v>学生只说「挺好的」</v>
+        <v>信息不足无法判定</v>
       </c>
       <c r="AD4" t="str">
-        <v>准备记录表</v>
+        <v>准备四象限图</v>
       </c>
       <c r="AE4" t="str">
-        <v>记录表</v>
+        <v>能力×意愿四象限图、四型策略表</v>
       </c>
       <c r="AF4" t="str">
-        <v>一次执行记录</v>
+        <v>个案诊断结论</v>
       </c>
       <c r="AG4" t="str">
         <v/>
       </c>
       <c r="AH4" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AI4" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
@@ -846,10 +846,10 @@
         <v>CS_RX_04</v>
       </c>
       <c r="B5" t="str">
-        <v>规则共构工作坊</v>
+        <v>班委选拔六步法</v>
       </c>
       <c r="C5" t="str">
-        <v>规则共构工作坊</v>
+        <v>班委选拔六步法</v>
       </c>
       <c r="D5" t="str">
         <v>class_system</v>
@@ -858,52 +858,52 @@
         <v>framework</v>
       </c>
       <c r="F5" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="G5" t="str">
         <v>teacher</v>
       </c>
       <c r="H5" t="str">
-        <v>规则只贴在墙上，学生不认同</v>
+        <v>开学第1周组建服务型班委</v>
       </c>
       <c r="I5" t="str">
         <v>medium</v>
       </c>
       <c r="J5" t="str">
-        <v>CS_AT_04;CS_AT_06</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="K5" t="str">
-        <v>规范系统薄弱;堰塞湖蓄积风险</v>
+        <v>组织架构空缺</v>
       </c>
       <c r="L5" t="str">
-        <v>class_system,environment,warning,dam</v>
+        <v>class_system,organization,structure</v>
       </c>
       <c r="M5" t="str">
-        <v>CS_S1D4</v>
+        <v>CS_S1D2;CS_S1D1</v>
       </c>
       <c r="N5" t="str">
-        <v>把规则从教师要求转成共同约定</v>
+        <v>选举-试用-考核，避免『选举即任命』</v>
       </c>
       <c r="O5" t="str">
-        <v>挑一条最常被违反的规则；让学生说出这条规则存在的理由，教师补充缺失的部分；一起把规则改写成可观察的行为描述；约定试行两周后复盘</v>
+        <v>岗位发布（开学前张贴，1-2年师生共议，3-6年自主申报）；自主报名；岗位答辩（1-2分钟说想做+怎么做）；试用考核（1周）；正式任命；月度培训赋能（8课时例会）</v>
       </c>
       <c r="P5" t="str">
-        <v>这条规则不是为了限制大家，而是为了让学习和相处更可预期。我们先试行三天再复盘。</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
-        <v>该规则违反次数下降 50% 以上</v>
+        <v>服务型班委组建，岗位覆盖率100%</v>
       </c>
       <c r="R5" t="str">
-        <v>一节班会</v>
+        <v>一节课</v>
       </c>
       <c r="S5" t="str">
-        <v>每月一条</v>
+        <v>开学第1周启动，月度例会</v>
       </c>
       <c r="T5" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U5" t="str">
-        <v>不要一次重构全部规则</v>
+        <v>不用于替代危机处置</v>
       </c>
       <c r="V5" t="str">
         <v/>
@@ -921,31 +921,31 @@
         <v>B</v>
       </c>
       <c r="AA5" t="str">
-        <v>班级系统建设手册 第5章</v>
+        <v>工作手册·第三章3.2</v>
       </c>
       <c r="AB5" t="str">
-        <v>两周内违反次数明显下降</v>
+        <v>班委履职打卡≥90%</v>
       </c>
       <c r="AC5" t="str">
-        <v>两周后无变化</v>
+        <v>无人报名或答辩流于形式</v>
       </c>
       <c r="AD5" t="str">
-        <v>准备记录表</v>
+        <v>准备岗位说明书</v>
       </c>
       <c r="AE5" t="str">
-        <v>记录表</v>
+        <v>岗位发布海报、答辩评价表</v>
       </c>
       <c r="AF5" t="str">
-        <v>一次执行记录</v>
+        <v>班委任命名单</v>
       </c>
       <c r="AG5" t="str">
         <v/>
       </c>
       <c r="AH5" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AI5" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
@@ -956,64 +956,64 @@
         <v>CS_RX_05</v>
       </c>
       <c r="B6" t="str">
-        <v>冲突修复四步法</v>
+        <v>班级公约制定六步法</v>
       </c>
       <c r="C6" t="str">
-        <v>冲突修复四步法</v>
+        <v>班级公约制定六步</v>
       </c>
       <c r="D6" t="str">
         <v>class_system</v>
       </c>
       <c r="E6" t="str">
-        <v>script</v>
+        <v>framework</v>
       </c>
       <c r="F6" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="G6" t="str">
         <v>teacher</v>
       </c>
       <c r="H6" t="str">
-        <v>学生冲突反复发生且难以修复</v>
+        <v>开学第2周民主制定班级规则（软规则）</v>
       </c>
       <c r="I6" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="J6" t="str">
-        <v>CS_AT_05;CS_AT_06</v>
+        <v>CS_AT_07</v>
       </c>
       <c r="K6" t="str">
-        <v>关系系统受损;堰塞湖蓄积风险</v>
+        <v>公约悬空</v>
       </c>
       <c r="L6" t="str">
-        <v>class_system,relation,warning,dam</v>
+        <v>class_system,norm,rules</v>
       </c>
       <c r="M6" t="str">
-        <v>CS_S1D5</v>
+        <v>CS_S1D3;CS_S1D1</v>
       </c>
       <c r="N6" t="str">
-        <v>建立可重复的冲突处理流程</v>
+        <v>软规则（公约）区别于硬制度，签约上墙增强『被制定感』</v>
       </c>
       <c r="O6" t="str">
-        <v>分开双方，各自说清「发生了什么」，只说事实；各自说「我当时的感受」，不评价对方；各自说「我希望接下来怎样」；共同确认一个可执行的下一步，并约定检查时间</v>
+        <v>案例收集；小组讨论；全班共商；草拟公约（8-12条）；签字上墙（师生签字）；执行评估（定期修订）</v>
       </c>
       <c r="P6" t="str">
-        <v>我们先不讨论谁对谁错，先把事实说清楚。</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
-        <v>同类冲突复发率下降</v>
+        <v>公约知晓率≥90%，违规复发率&lt;20%</v>
       </c>
       <c r="R6" t="str">
-        <v>20 分钟</v>
+        <v>两节课</v>
       </c>
       <c r="S6" t="str">
-        <v>按需</v>
+        <v>开学第2周，月度修订</v>
       </c>
       <c r="T6" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U6" t="str">
-        <v>不要在全班面前处理个体冲突</v>
+        <v>不用于替代危机处置</v>
       </c>
       <c r="V6" t="str">
         <v/>
@@ -1028,34 +1028,34 @@
         <v/>
       </c>
       <c r="Z6" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AA6" t="str">
-        <v>修复式实践在班级管理中的应用</v>
+        <v>工作手册·第五章5.2 / 第十章10.2</v>
       </c>
       <c r="AB6" t="str">
-        <v>双方均能说出对方的诉求</v>
+        <v>学生能说出公约条款</v>
       </c>
       <c r="AC6" t="str">
-        <v>任一方拒绝进入流程</v>
+        <v>公约上墙后无人知晓</v>
       </c>
       <c r="AD6" t="str">
-        <v>准备记录表</v>
+        <v>准备公约草案</v>
       </c>
       <c r="AE6" t="str">
-        <v>记录表</v>
+        <v>公约墙模板、签字上墙版</v>
       </c>
       <c r="AF6" t="str">
-        <v>一次执行记录</v>
+        <v>班级公约</v>
       </c>
       <c r="AG6" t="str">
         <v/>
       </c>
       <c r="AH6" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AI6" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
@@ -1066,121 +1066,2871 @@
         <v>CS_RX_06</v>
       </c>
       <c r="B7" t="str">
-        <v>同伴互助配对表</v>
+        <v>同伴冲突调解·修复性对话</v>
       </c>
       <c r="C7" t="str">
-        <v>同伴互助配对表</v>
+        <v>同伴冲突调解·修</v>
       </c>
       <c r="D7" t="str">
         <v>class_system</v>
       </c>
       <c r="E7" t="str">
-        <v>worksheet</v>
+        <v>script</v>
       </c>
       <c r="F7" t="str">
-        <v>all</v>
+        <v>primary</v>
       </c>
       <c r="G7" t="str">
         <v>teacher</v>
       </c>
       <c r="H7" t="str">
-        <v>班级缺少稳定的同伴支持结构</v>
+        <v>学生打闹/告状/冲突后的关系修复</v>
       </c>
       <c r="I7" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="J7" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_02;CS_AT_15</v>
       </c>
       <c r="K7" t="str">
-        <v>关系系统受损</v>
+        <v>同伴联结薄弱;归属感缺失</v>
       </c>
       <c r="L7" t="str">
-        <v>class_system,relation</v>
+        <v>class_system,relationship,peer,emotion,belonging</v>
       </c>
       <c r="M7" t="str">
-        <v>CS_S1D5</v>
+        <v>CS_S1D1</v>
       </c>
       <c r="N7" t="str">
-        <v>建立可持续的同伴互助关系</v>
+        <v>聚焦修复而非追责，是关系修复与文化生成的关键技术</v>
       </c>
       <c r="O7" t="str">
-        <v>按学习和性格互补原则做两两配对；给每对一个具体的互助任务，如每天互查作业；每周收一次简短反馈，只问「这周互相帮到了什么」；两周后按反馈调整配对</v>
+        <v>分开冷静；各自陈述（事实-影响-感受）；修复性对话（你做了什么/影响了谁/怎么修复）；达成修复约定；跟进复盘</v>
       </c>
       <c r="P7" t="str">
-        <v>你们两个这周互相提醒一下，周五我来听听你们互相帮到了什么。</v>
+        <v>我们先不讨论谁对谁错，先把事实说清楚：发生了什么？影响了谁？你觉得可以怎么修复？</v>
       </c>
       <c r="Q7" t="str">
-        <v>被孤立学生数量下降</v>
+        <v>同类冲突复发率下降，调解成功率≥80%</v>
       </c>
       <c r="R7" t="str">
         <v>20 分钟</v>
       </c>
       <c r="S7" t="str">
-        <v>每月调整一次</v>
+        <v>按需</v>
       </c>
       <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v>涉及欺凌或安全事件时不适用同伴调解，须启动危机响应流程</v>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>技术手册·第七部分危机响应</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>双方达成修复约定并执行</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>任一方拒绝进入流程</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>准备话术卡</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>修复性对话话术卡</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>修复约定记录</v>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>师生连接技术</v>
+      </c>
+      <c r="C8" t="str">
+        <v>师生连接技术</v>
+      </c>
+      <c r="D8" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E8" t="str">
+        <v>script</v>
+      </c>
+      <c r="F8" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G8" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H8" t="str">
+        <v>师生沟通、学生情绪、家长沟通中的连接建立</v>
+      </c>
+      <c r="I8" t="str">
+        <v>low</v>
+      </c>
+      <c r="J8" t="str">
+        <v>CS_AT_01;CS_AT_14</v>
+      </c>
+      <c r="K8" t="str">
+        <v>亲师依恋断裂;个体情绪失接</v>
+      </c>
+      <c r="L8" t="str">
+        <v>class_system,relationship,attachment,emotion,support</v>
+      </c>
+      <c r="M8" t="str">
+        <v>CS_S1D1;CS_S1D5</v>
+      </c>
+      <c r="N8" t="str">
+        <v>73855/意义换框/EQ为密码本教师核心技术</v>
+      </c>
+      <c r="O8" t="str">
+        <v>73855法则（7%文字/38%语调/55%肢体，70%积极+30%待改进）；意义换框（把『下滑』重构为『成长课题』）；EQ四步（停-听-标-析-选）</v>
+      </c>
+      <c r="P8" t="str">
+        <v>听起来你现在很（情绪），是吗？（先跟）那对你最重要的是什么？（上堆）我们可以做哪些尝试？（后带）</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>师生连接增强，对抗减少</v>
+      </c>
+      <c r="R8" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S8" t="str">
+        <v>日常持续</v>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>技术手册·第十六/十八部分</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>学生愿意表达与求助</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>多次尝试仍对抗</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>熟悉73855法则</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>73855自评表、意义换框练习册、EQ四步海报</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>沟通记录</v>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>依恋关系干预技术</v>
+      </c>
+      <c r="C9" t="str">
+        <v>依恋关系干预技术</v>
+      </c>
+      <c r="D9" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E9" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F9" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G9" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H9" t="str">
+        <v>安全/A(回避)/B(焦虑)/C(抗拒)/D(混乱)五型学生的差异化干预</v>
+      </c>
+      <c r="I9" t="str">
+        <v>high</v>
+      </c>
+      <c r="J9" t="str">
+        <v>CS_AT_01</v>
+      </c>
+      <c r="K9" t="str">
+        <v>亲师依恋断裂</v>
+      </c>
+      <c r="L9" t="str">
+        <v>class_system,relationship,attachment</v>
+      </c>
+      <c r="M9" t="str">
+        <v>CS_S1D1</v>
+      </c>
+      <c r="N9" t="str">
+        <v>补偿性安全基地：教师可部分弥补不安全家庭依恋</v>
+      </c>
+      <c r="O9" t="str">
+        <v>安全型：维持安全基地；A型（回避）：主动靠近+低压力邀请；B型（焦虑）：可预测回应+稳定陪伴；C型（抗拒）：先连接情绪再提要求；D型（混乱）：优先建安全感，1个工作日内转介心理专业</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>主动求助≥2次/周，谈心覆盖率100%</v>
+      </c>
+      <c r="R9" t="str">
+        <v>按型别</v>
+      </c>
+      <c r="S9" t="str">
+        <v>4-6周/轮</v>
+      </c>
+      <c r="T9" t="str">
         <v>30</v>
       </c>
-      <c r="U7" t="str">
-        <v>不要把配对当成优生帮差生的单向安排</v>
-      </c>
-      <c r="V7" t="str">
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <v/>
-      </c>
-      <c r="X7" t="str">
-        <v/>
-      </c>
-      <c r="Y7" t="str">
-        <v/>
-      </c>
-      <c r="Z7" t="str">
-        <v>C</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>同伴支持机制实务</v>
-      </c>
-      <c r="AB7" t="str">
-        <v>80% 配对能说出互助内容</v>
-      </c>
-      <c r="AC7" t="str">
-        <v>半数配对无实际互动</v>
-      </c>
-      <c r="AD7" t="str">
-        <v>准备记录表</v>
-      </c>
-      <c r="AE7" t="str">
-        <v>记录表</v>
-      </c>
-      <c r="AF7" t="str">
-        <v>一次执行记录</v>
-      </c>
-      <c r="AG7" t="str">
-        <v/>
-      </c>
-      <c r="AH7" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-      <c r="AI7" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AJ7" t="str">
+      <c r="U9" t="str">
+        <v>D型（混乱）须1个工作日内转介心理专业，不要独自长时间处理</v>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>技术手册·第十九部分19.3</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>回避/对抗行为下降</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>D型未及时转介</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>完成依恋关系观察清单评估</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>依恋类型识别卡、转介沟通话术</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>依恋干预记录</v>
+      </c>
+      <c r="AG9" t="str">
+        <v/>
+      </c>
+      <c r="AH9" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_RX_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>班级团建与仪式感活动</v>
+      </c>
+      <c r="C10" t="str">
+        <v>班级团建与仪式感</v>
+      </c>
+      <c r="D10" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E10" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F10" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G10" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H10" t="str">
+        <v>关系激活期凝聚力建设</v>
+      </c>
+      <c r="I10" t="str">
+        <v>low</v>
+      </c>
+      <c r="J10" t="str">
+        <v>CS_AT_15;CS_AT_13;CS_AT_02</v>
+      </c>
+      <c r="K10" t="str">
+        <v>归属感缺失;氛围负向;同伴联结薄弱</v>
+      </c>
+      <c r="L10" t="str">
+        <v>class_system,emotion,belonging,climate,relationship,peer</v>
+      </c>
+      <c r="M10" t="str">
+        <v>CS_S1D1;CS_S1D5</v>
+      </c>
+      <c r="N10" t="str">
+        <v>仪式感是正向氛围的稳定器</v>
+      </c>
+      <c r="O10" t="str">
+        <v>周仪式（晨圈/点赞）；月度团建；混搭座位+小组任务；夸夸墙</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>低参与学生归零，主动发言≥1次/周</v>
+      </c>
+      <c r="R10" t="str">
+        <v>每周30分钟</v>
+      </c>
+      <c r="S10" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>工作手册·文化建设</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>参与率提升</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>活动后无复盘、参与度持续走低</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>准备活动清单</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>团建活动清单、仪式设计模板</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>活动记录</v>
+      </c>
+      <c r="AG10" t="str">
+        <v/>
+      </c>
+      <c r="AH10" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_RX_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>班委架构搭建</v>
+      </c>
+      <c r="C11" t="str">
+        <v>班委架构搭建</v>
+      </c>
+      <c r="D11" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E11" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F11" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G11" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H11" t="str">
+        <v>班级组织运转、责任分散</v>
+      </c>
+      <c r="I11" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J11" t="str">
+        <v>CS_AT_04;CS_AT_06</v>
+      </c>
+      <c r="K11" t="str">
+        <v>组织架构空缺;运转机制失效</v>
+      </c>
+      <c r="L11" t="str">
+        <v>class_system,organization,structure,operation</v>
+      </c>
+      <c r="M11" t="str">
+        <v>CS_S1D2</v>
+      </c>
+      <c r="N11" t="str">
+        <v>重塑角色定义（服务而非管），降低『怕得罪人/形同虚设』</v>
+      </c>
+      <c r="O11" t="str">
+        <v>1个大管家（班委）+1个小管家（全班轮值）；2个长期岗位+2个短期项目；区块长制（人人有事做，事事有人管）</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v>岗位覆盖率100%，事务响应&lt;24h</v>
+      </c>
+      <c r="R11" t="str">
+        <v>一节课</v>
+      </c>
+      <c r="S11" t="str">
+        <v>学期初搭建，每月微调</v>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>工作手册·第三章3.1</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>人人有事做、事事有人管</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>核心岗位空缺超过1周</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>准备分工表</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>班委架构图、区块长分工表</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>班委架构图</v>
+      </c>
+      <c r="AG11" t="str">
+        <v/>
+      </c>
+      <c r="AH11" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_RX_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>岗位认领与轮换</v>
+      </c>
+      <c r="C12" t="str">
+        <v>岗位认领与轮换</v>
+      </c>
+      <c r="D12" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E12" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F12" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G12" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H12" t="str">
+        <v>责任岗位长期真空或集中个别人</v>
+      </c>
+      <c r="I12" t="str">
+        <v>low</v>
+      </c>
+      <c r="J12" t="str">
+        <v>CS_AT_04;CS_AT_06</v>
+      </c>
+      <c r="K12" t="str">
+        <v>组织架构空缺;运转机制失效</v>
+      </c>
+      <c r="L12" t="str">
+        <v>class_system,organization,structure,operation</v>
+      </c>
+      <c r="M12" t="str">
+        <v>CS_S1D2</v>
+      </c>
+      <c r="N12" t="str">
+        <v>避免责任岗位真空或集中在个别人</v>
+      </c>
+      <c r="O12" t="str">
+        <v>长期岗学期初选，稳定运行；短期项目按需发布；轮值制让每人有机会；每月扩展1项新责任</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v>岗位覆盖率提升，责任分散</v>
+      </c>
+      <c r="R12" t="str">
+        <v>20 分钟</v>
+      </c>
+      <c r="S12" t="str">
+        <v>每月扩展1项</v>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>工作手册·第三章3.3</v>
+      </c>
+      <c r="AB12" t="str">
+        <v>每人至少1个责任岗位</v>
+      </c>
+      <c r="AC12" t="str">
+        <v>岗位长期无人认领</v>
+      </c>
+      <c r="AD12" t="str">
+        <v>准备认领表</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>岗位认领表、轮换日历</v>
+      </c>
+      <c r="AF12" t="str">
+        <v>岗位认领表</v>
+      </c>
+      <c r="AG12" t="str">
+        <v/>
+      </c>
+      <c r="AH12" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI12" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_RX_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>座位编排SOP</v>
+      </c>
+      <c r="C13" t="str">
+        <v>座位编排SOP</v>
+      </c>
+      <c r="D13" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E13" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F13" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G13" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H13" t="str">
+        <v>座位调整（小学敏感动作，需透明有依据）</v>
+      </c>
+      <c r="I13" t="str">
+        <v>low</v>
+      </c>
+      <c r="J13" t="str">
+        <v>CS_AT_05</v>
+      </c>
+      <c r="K13" t="str">
+        <v>架构适配失当</v>
+      </c>
+      <c r="L13" t="str">
+        <v>class_system,organization,seating</v>
+      </c>
+      <c r="M13" t="str">
+        <v>CS_S1D2</v>
+      </c>
+      <c r="N13" t="str">
+        <v>按特质与关系分组，避免排座冲突与搭便车</v>
+      </c>
+      <c r="O13" t="str">
+        <v>明确原则（身高+视力+男女混搭+性格互补+小组合作便利）；拟方案→班级共商→确定；自评座位满意度；每学期调整1-2次</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v>组内贡献方差下降，冲突≤1次/周</v>
+      </c>
+      <c r="R13" t="str">
+        <v>一节课</v>
+      </c>
+      <c r="S13" t="str">
+        <v>每学期1-2次</v>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v>座位调整需透明有依据，先共商再执行，避免学生产生不公感</v>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>工作手册·第十一章11.1.3</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>座位满意度自评达标</v>
+      </c>
+      <c r="AC13" t="str">
+        <v>排座引发冲突</v>
+      </c>
+      <c r="AD13" t="str">
+        <v>收集学生意见</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>座位编排模板、满意度自评表</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>座位表</v>
+      </c>
+      <c r="AG13" t="str">
+        <v/>
+      </c>
+      <c r="AH13" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI13" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_RX_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Kagan合作学习结构</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Kagan合作学</v>
+      </c>
+      <c r="D14" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E14" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F14" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G14" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H14" t="str">
+        <v>课堂合作、打破小团体、提升参与度</v>
+      </c>
+      <c r="I14" t="str">
+        <v>low</v>
+      </c>
+      <c r="J14" t="str">
+        <v>CS_AT_02;CS_AT_05</v>
+      </c>
+      <c r="K14" t="str">
+        <v>同伴联结薄弱;架构适配失当</v>
+      </c>
+      <c r="L14" t="str">
+        <v>class_system,relationship,peer,organization,seating</v>
+      </c>
+      <c r="M14" t="str">
+        <v>CS_S1D2;CS_S1D1</v>
+      </c>
+      <c r="N14" t="str">
+        <v>结构化合作，解决少数人发言/搭便车/闲聊三大弊病</v>
+      </c>
+      <c r="O14" t="str">
+        <v>时钟伙伴（12/3/6/9点找不同伙伴，自然打破小团体）；PIES原则（正向互赖/个体责任/平等参与/同时互动）；从1分钟逐步加长</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v>小组参与均衡，小团体被打破</v>
+      </c>
+      <c r="R14" t="str">
+        <v>课堂内嵌</v>
+      </c>
+      <c r="S14" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>技术手册·第十三部分（Kagan）</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>全员参与率提升</v>
+      </c>
+      <c r="AC14" t="str">
+        <v>合作流于形式</v>
+      </c>
+      <c r="AD14" t="str">
+        <v>设计时钟伙伴分组</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>时钟伙伴地面标识、PIES检查表</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>合作任务记录</v>
+      </c>
+      <c r="AG14" t="str">
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI14" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_RX_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>班规共创与执行评估</v>
+      </c>
+      <c r="C15" t="str">
+        <v>班规共创与执行评</v>
+      </c>
+      <c r="D15" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E15" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F15" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G15" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H15" t="str">
+        <v>规则执行乏力、需定期修订</v>
+      </c>
+      <c r="I15" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J15" t="str">
+        <v>CS_AT_07;CS_AT_08</v>
+      </c>
+      <c r="K15" t="str">
+        <v>公约悬空;督导标准不一</v>
+      </c>
+      <c r="L15" t="str">
+        <v>class_system,norm,rules,supervision</v>
+      </c>
+      <c r="M15" t="str">
+        <v>CS_S1D3</v>
+      </c>
+      <c r="N15" t="str">
+        <v>把规则从教师要求转成共同约定并持续评估</v>
+      </c>
+      <c r="O15" t="str">
+        <v>共识复盘（每月）；执行评估（达标/修订）；配套五星点检；修订启动（制度自转期）</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v>规则执行一致性提升，违规复发率&lt;20%</v>
+      </c>
+      <c r="R15" t="str">
+        <v>一节班会</v>
+      </c>
+      <c r="S15" t="str">
+        <v>每月</v>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>工作手册·第五章5.2</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>违规复发率下降</v>
+      </c>
+      <c r="AC15" t="str">
+        <v>修订后仍无人知晓</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>准备评估表</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>班规执行评估表</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>班规执行评估表</v>
+      </c>
+      <c r="AG15" t="str">
+        <v/>
+      </c>
+      <c r="AH15" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI15" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_RX_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>行为规范督导</v>
+      </c>
+      <c r="C16" t="str">
+        <v>行为规范督导</v>
+      </c>
+      <c r="D16" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E16" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F16" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G16" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H16" t="str">
+        <v>行为系统日常督导</v>
+      </c>
+      <c r="I16" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J16" t="str">
+        <v>CS_AT_08</v>
+      </c>
+      <c r="K16" t="str">
+        <v>督导标准不一</v>
+      </c>
+      <c r="L16" t="str">
+        <v>class_system,norm,supervision</v>
+      </c>
+      <c r="M16" t="str">
+        <v>CS_S1D3</v>
+      </c>
+      <c r="N16" t="str">
+        <v>三级点检网络统一督导标准</v>
+      </c>
+      <c r="O16" t="str">
+        <v>日点检（班委/值日班长）；周点检（班主任）；月反馈（家长/五星）；三级网络覆盖五维度</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v>处置一致性≥90%</v>
+      </c>
+      <c r="R16" t="str">
+        <v>每日3分钟</v>
+      </c>
+      <c r="S16" t="str">
+        <v>日周月循环</v>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>工作手册·第十二章12.2</v>
+      </c>
+      <c r="AB16" t="str">
+        <v>同行为处置差异≤2级</v>
+      </c>
+      <c r="AC16" t="str">
+        <v>点检流于形式</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>公布行为清单与处置标准</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>三级点检记录表、日周月反馈模板</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>三级点检记录</v>
+      </c>
+      <c r="AG16" t="str">
+        <v/>
+      </c>
+      <c r="AH16" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI16" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_RX_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>五星正向评价</v>
+      </c>
+      <c r="C17" t="str">
+        <v>五星正向评价</v>
+      </c>
+      <c r="D17" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E17" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F17" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G17" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H17" t="str">
+        <v>德育常规/学风管理/家校共育评价</v>
+      </c>
+      <c r="I17" t="str">
+        <v>low</v>
+      </c>
+      <c r="J17" t="str">
+        <v>CS_AT_08;CS_AT_13</v>
+      </c>
+      <c r="K17" t="str">
+        <v>督导标准不一;氛围负向</v>
+      </c>
+      <c r="L17" t="str">
+        <v>class_system,norm,supervision,emotion,climate</v>
+      </c>
+      <c r="M17" t="str">
+        <v>CS_S1D3;CS_S1D5</v>
+      </c>
+      <c r="N17" t="str">
+        <v>引自学校《六力小学班级系统建设制度》</v>
+      </c>
+      <c r="O17" t="str">
+        <v>德育常规1-5星；学风管理1-5星；家校共育1-5星；班主任为第一责任人；月度评定，9/12/15星→三/四/五星班级</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v>正向评价体系落地，氛围评分≥4.0</v>
+      </c>
+      <c r="R17" t="str">
+        <v>月度评定</v>
+      </c>
+      <c r="S17" t="str">
+        <v>每月</v>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V17" t="str">
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>学校《六力小学班级系统建设制度》（工作手册引）</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>月度评定完成</v>
+      </c>
+      <c r="AC17" t="str">
+        <v>评定无依据或流于形式</v>
+      </c>
+      <c r="AD17" t="str">
+        <v>熟悉五星标准</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>五星点检标准</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>五星评定表</v>
+      </c>
+      <c r="AG17" t="str">
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_RX_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>班主任一日工作SOP</v>
+      </c>
+      <c r="C18" t="str">
+        <v>班主任一日工作S</v>
+      </c>
+      <c r="D18" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E18" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F18" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G18" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H18" t="str">
+        <v>每日工作节奏把控</v>
+      </c>
+      <c r="I18" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J18" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="K18" t="str">
+        <v>运转机制失效</v>
+      </c>
+      <c r="L18" t="str">
+        <v>class_system,organization,operation</v>
+      </c>
+      <c r="M18" t="str">
+        <v>CS_S1D3;CS_S1D2</v>
+      </c>
+      <c r="N18" t="str">
+        <v>把每日事务转成固定节奏，降低教师负担</v>
+      </c>
+      <c r="O18" t="str">
+        <v>「三个1分钟」（课前组织/课中每15分钟巡视/课后小结）；早读-课间-眼保健操-午餐-放学节点；周班会（班委主舞台，班主任导演）</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v>常规事务响应&lt;24h，积压=0</v>
+      </c>
+      <c r="R18" t="str">
+        <v>全天</v>
+      </c>
+      <c r="S18" t="str">
+        <v>每日</v>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>工作手册·第六章6.1</v>
+      </c>
+      <c r="AB18" t="str">
+        <v>节点执行无遗漏</v>
+      </c>
+      <c r="AC18" t="str">
+        <v>节奏被打乱后无法恢复</v>
+      </c>
+      <c r="AD18" t="str">
+        <v>制定个人时段表</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>一日流程时段表</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>一日流程时段表</v>
+      </c>
+      <c r="AG18" t="str">
+        <v/>
+      </c>
+      <c r="AH18" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI18" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_RX_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>班级愿景共建</v>
+      </c>
+      <c r="C19" t="str">
+        <v>班级愿景共建</v>
+      </c>
+      <c r="D19" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E19" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F19" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G19" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H19" t="str">
+        <v>目标系统建设、班级方向感</v>
+      </c>
+      <c r="I19" t="str">
+        <v>low</v>
+      </c>
+      <c r="J19" t="str">
+        <v>CS_AT_10</v>
+      </c>
+      <c r="K19" t="str">
+        <v>目标缺位</v>
+      </c>
+      <c r="L19" t="str">
+        <v>class_system,goal,target</v>
+      </c>
+      <c r="M19" t="str">
+        <v>CS_S1D4</v>
+      </c>
+      <c r="N19" t="str">
+        <v>把抽象目标转成可观察的班级共识</v>
+      </c>
+      <c r="O19" t="str">
+        <v>师生共议『班级想要的样子』；凝练班名/口号/班级目标；上墙可视化</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v>目标覆盖率≥90%，达成率≥70%</v>
+      </c>
+      <c r="R19" t="str">
+        <v>一节班会</v>
+      </c>
+      <c r="S19" t="str">
+        <v>每学期一次</v>
+      </c>
+      <c r="T19" t="str">
+        <v>90</v>
+      </c>
+      <c r="U19" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V19" t="str">
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>工作手册·文化建设</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>学生能说出班级目标</v>
+      </c>
+      <c r="AC19" t="str">
+        <v>目标只停留在口号</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>准备引导卡</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>愿景共创引导卡</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>班级愿景墙</v>
+      </c>
+      <c r="AG19" t="str">
+        <v/>
+      </c>
+      <c r="AH19" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI19" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CS_RX_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>个人目标卡与成长档案袋</v>
+      </c>
+      <c r="C20" t="str">
+        <v>个人目标卡与成长</v>
+      </c>
+      <c r="D20" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E20" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F20" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G20" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H20" t="str">
+        <v>学生个人发展目标管理</v>
+      </c>
+      <c r="I20" t="str">
+        <v>low</v>
+      </c>
+      <c r="J20" t="str">
+        <v>CS_AT_11;CS_AT_10</v>
+      </c>
+      <c r="K20" t="str">
+        <v>动力错配;目标缺位</v>
+      </c>
+      <c r="L20" t="str">
+        <v>class_system,goal,motivation,target</v>
+      </c>
+      <c r="M20" t="str">
+        <v>CS_S1D4</v>
+      </c>
+      <c r="N20" t="str">
+        <v>用目标卡+档案袋让成长可见</v>
+      </c>
+      <c r="O20" t="str">
+        <v>学期初设个人目标卡；过程记录（档案袋：文字+数据+反思）；家长会/展示日呈现</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v>个人目标达成率提升，自主任务发起≥2次/周</v>
+      </c>
+      <c r="R20" t="str">
+        <v>20 分钟</v>
+      </c>
+      <c r="S20" t="str">
+        <v>学期制</v>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V20" t="str">
+        <v/>
+      </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>技术手册·成长档案袋</v>
+      </c>
+      <c r="AB20" t="str">
+        <v>档案袋有过程记录</v>
+      </c>
+      <c r="AC20" t="str">
+        <v>目标卡填完即弃</v>
+      </c>
+      <c r="AD20" t="str">
+        <v>准备目标卡</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>目标卡模板、档案袋模板</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>个人目标卡/档案袋</v>
+      </c>
+      <c r="AG20" t="str">
+        <v/>
+      </c>
+      <c r="AH20" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI20" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CS_RX_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>目标墙与进度追踪</v>
+      </c>
+      <c r="C21" t="str">
+        <v>目标墙与进度追踪</v>
+      </c>
+      <c r="D21" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E21" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F21" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G21" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H21" t="str">
+        <v>目标可视化、持续动力</v>
+      </c>
+      <c r="I21" t="str">
+        <v>low</v>
+      </c>
+      <c r="J21" t="str">
+        <v>CS_AT_10</v>
+      </c>
+      <c r="K21" t="str">
+        <v>目标缺位</v>
+      </c>
+      <c r="L21" t="str">
+        <v>class_system,goal,target</v>
+      </c>
+      <c r="M21" t="str">
+        <v>CS_S1D4</v>
+      </c>
+      <c r="N21" t="str">
+        <v>可视化让目标从墙上走进日常</v>
+      </c>
+      <c r="O21" t="str">
+        <v>目标墙张贴；进度贴纸标记；月度复盘会</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v>目标进度可见，持续动力</v>
+      </c>
+      <c r="R21" t="str">
+        <v>月度复盘20分钟</v>
+      </c>
+      <c r="S21" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA21" t="str">
+        <v>工作手册·文化建设</v>
+      </c>
+      <c r="AB21" t="str">
+        <v>月度复盘会常态化</v>
+      </c>
+      <c r="AC21" t="str">
+        <v>目标墙无人更新</v>
+      </c>
+      <c r="AD21" t="str">
+        <v>设计目标墙</v>
+      </c>
+      <c r="AE21" t="str">
+        <v>目标墙模板、进度贴纸</v>
+      </c>
+      <c r="AF21" t="str">
+        <v>目标墙</v>
+      </c>
+      <c r="AG21" t="str">
+        <v/>
+      </c>
+      <c r="AH21" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI21" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CS_RX_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>情绪角设置</v>
+      </c>
+      <c r="C22" t="str">
+        <v>情绪角设置</v>
+      </c>
+      <c r="D22" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E22" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F22" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G22" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H22" t="str">
+        <v>学生情绪失控、需安全空间</v>
+      </c>
+      <c r="I22" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J22" t="str">
+        <v>CS_AT_14</v>
+      </c>
+      <c r="K22" t="str">
+        <v>个体情绪失接</v>
+      </c>
+      <c r="L22" t="str">
+        <v>class_system,emotion,support</v>
+      </c>
+      <c r="M22" t="str">
+        <v>CS_S1D5</v>
+      </c>
+      <c r="N22" t="str">
+        <v>给情绪一个安全出口</v>
+      </c>
+      <c r="O22" t="str">
+        <v>设安全角（软垫/绘本/情绪卡）；建安全信号（举手求助）；允许短暂休息但明确『休息后回来继续』；频率过高（周&gt;3次）转介心理</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v>情绪角周使用≥3人，情绪失接减少</v>
+      </c>
+      <c r="R22" t="str">
+        <v>10 分钟/次</v>
+      </c>
+      <c r="S22" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v>使用频率过高（每周超过3次）须转介心理教师，不能只靠情绪角</v>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>技术手册·积极心理</v>
+      </c>
+      <c r="AB22" t="str">
+        <v>情绪角正常使用</v>
+      </c>
+      <c r="AC22" t="str">
+        <v>周使用&gt;3次（提示需转介）</v>
+      </c>
+      <c r="AD22" t="str">
+        <v>布置情绪角</v>
+      </c>
+      <c r="AE22" t="str">
+        <v>情绪角布置清单、情绪卡片</v>
+      </c>
+      <c r="AF22" t="str">
+        <v>情绪角使用记录</v>
+      </c>
+      <c r="AG22" t="str">
+        <v/>
+      </c>
+      <c r="AH22" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI22" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_RX_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>正念练习</v>
+      </c>
+      <c r="C23" t="str">
+        <v>正念练习</v>
+      </c>
+      <c r="D23" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E23" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F23" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G23" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H23" t="str">
+        <v>注意力、情绪调节、课堂静定</v>
+      </c>
+      <c r="I23" t="str">
+        <v>low</v>
+      </c>
+      <c r="J23" t="str">
+        <v>CS_AT_13;CS_AT_14</v>
+      </c>
+      <c r="K23" t="str">
+        <v>氛围负向;个体情绪失接</v>
+      </c>
+      <c r="L23" t="str">
+        <v>class_system,emotion,climate,support</v>
+      </c>
+      <c r="M23" t="str">
+        <v>CS_S1D5</v>
+      </c>
+      <c r="N23" t="str">
+        <v>对外可称『注意力训练』降低家长误解</v>
+      </c>
+      <c r="O23" t="str">
+        <v>葡萄干练习（30秒观察一颗）；呼吸计时器（3分钟『大脑充电器』）；时段表（晨间/课前/午后）；从1分钟逐步加到3分钟</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v>课堂静定、注意力提升</v>
+      </c>
+      <c r="R23" t="str">
+        <v>1-3 分钟</v>
+      </c>
+      <c r="S23" t="str">
+        <v>每日固定时段</v>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA23" t="str">
+        <v>技术手册·第十二部分（正念）</v>
+      </c>
+      <c r="AB23" t="str">
+        <v>班级静定时间增长</v>
+      </c>
+      <c r="AC23" t="str">
+        <v>学生抗拒练习</v>
+      </c>
+      <c r="AD23" t="str">
+        <v>教师先行练习</v>
+      </c>
+      <c r="AE23" t="str">
+        <v>正念时段表、呼吸计时器APP</v>
+      </c>
+      <c r="AF23" t="str">
+        <v>正念时段记录</v>
+      </c>
+      <c r="AG23" t="str">
+        <v/>
+      </c>
+      <c r="AH23" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI23" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_RX_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>VIA品格优势培育</v>
+      </c>
+      <c r="C24" t="str">
+        <v>VIA品格优势培</v>
+      </c>
+      <c r="D24" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E24" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F24" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G24" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H24" t="str">
+        <v>积极心理、品格发展</v>
+      </c>
+      <c r="I24" t="str">
+        <v>low</v>
+      </c>
+      <c r="J24" t="str">
+        <v>CS_AT_13;CS_AT_15</v>
+      </c>
+      <c r="K24" t="str">
+        <v>氛围负向;归属感缺失</v>
+      </c>
+      <c r="L24" t="str">
+        <v>class_system,emotion,climate,belonging</v>
+      </c>
+      <c r="M24" t="str">
+        <v>CS_S1D5</v>
+      </c>
+      <c r="N24" t="str">
+        <v>与SDQ互补：SDQ查『困难』，VIA查『优势』</v>
+      </c>
+      <c r="O24" t="str">
+        <v>6项小学重点（创造力/勇敢/仁爱/公平/领导力/好奇）；12项优势卡；发现-命名-强化话术；学科渗透（语文渗善良/数学渗坚持）</v>
+      </c>
+      <c r="P24" t="str">
+        <v>看到小X主动帮助（发现），这是责任优势（命名），为你骄傲（强化）</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>品格优势被看见，正向氛围提升</v>
+      </c>
+      <c r="R24" t="str">
+        <v>每周1次</v>
+      </c>
+      <c r="S24" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+      <c r="Z24" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA24" t="str">
+        <v>技术手册·第十五部分（VIA/Seligman）</v>
+      </c>
+      <c r="AB24" t="str">
+        <v>学生能说出自己的优势</v>
+      </c>
+      <c r="AC24" t="str">
+        <v>流于表扬没有命名强化</v>
+      </c>
+      <c r="AD24" t="str">
+        <v>准备优势卡</v>
+      </c>
+      <c r="AE24" t="str">
+        <v>VIA 12项小学版核心优势卡</v>
+      </c>
+      <c r="AF24" t="str">
+        <v>优势卡记录</v>
+      </c>
+      <c r="AG24" t="str">
+        <v/>
+      </c>
+      <c r="AH24" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI24" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_RX_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>感恩与赞美仪式</v>
+      </c>
+      <c r="C25" t="str">
+        <v>感恩与赞美仪式</v>
+      </c>
+      <c r="D25" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E25" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F25" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G25" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H25" t="str">
+        <v>情感连接、正向氛围</v>
+      </c>
+      <c r="I25" t="str">
+        <v>low</v>
+      </c>
+      <c r="J25" t="str">
+        <v>CS_AT_13;CS_AT_15</v>
+      </c>
+      <c r="K25" t="str">
+        <v>氛围负向;归属感缺失</v>
+      </c>
+      <c r="L25" t="str">
+        <v>class_system,emotion,climate,belonging</v>
+      </c>
+      <c r="M25" t="str">
+        <v>CS_S1D5</v>
+      </c>
+      <c r="N25" t="str">
+        <v>仪式感是班级温度的建设器</v>
+      </c>
+      <c r="O25" t="str">
+        <v>每日点赞；夸夸墙；发现-命名-强化话术</v>
+      </c>
+      <c r="P25" t="str">
+        <v>看到小X主动帮助（发现），这是责任优势（命名），为你骄傲（强化）</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>正向氛围提升，月度氛围评分≥4.0</v>
+      </c>
+      <c r="R25" t="str">
+        <v>每日3分钟</v>
+      </c>
+      <c r="S25" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <v/>
+      </c>
+      <c r="Z25" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA25" t="str">
+        <v>工作手册/技术手册</v>
+      </c>
+      <c r="AB25" t="str">
+        <v>每日有点赞发生</v>
+      </c>
+      <c r="AC25" t="str">
+        <v>流于形式</v>
+      </c>
+      <c r="AD25" t="str">
+        <v>设置夸夸墙</v>
+      </c>
+      <c r="AE25" t="str">
+        <v>夸夸墙模板、优势命名话术</v>
+      </c>
+      <c r="AF25" t="str">
+        <v>夸夸墙</v>
+      </c>
+      <c r="AG25" t="str">
+        <v/>
+      </c>
+      <c r="AH25" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI25" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>心理风险A-E响应SOP</v>
+      </c>
+      <c r="C26" t="str">
+        <v>心理风险A-E响</v>
+      </c>
+      <c r="D26" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E26" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F26" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G26" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H26" t="str">
+        <v>心理危机五级分级响应</v>
+      </c>
+      <c r="I26" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="J26" t="str">
+        <v>CS_AT_09</v>
+      </c>
+      <c r="K26" t="str">
+        <v>危机响应迟滞</v>
+      </c>
+      <c r="L26" t="str">
+        <v>class_system,norm,crisis</v>
+      </c>
+      <c r="M26" t="str">
+        <v>CS_S1D3</v>
+      </c>
+      <c r="N26" t="str">
+        <v>A-E五级响应流程，框架参照六力小学制度</v>
+      </c>
+      <c r="O26" t="str">
+        <v>A级（安全事件）即时处置；B级（高风险：欺凌/自伤）2h内班主任+心理+家长；C级（中度）1周约谈+班级支持；D级（轻度）1月家校沟通；E级（健康）月度追踪；A/B级24-48h上报</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v>C级24h内启动率100%，漏报=0</v>
+      </c>
+      <c r="R26" t="str">
+        <v>即时</v>
+      </c>
+      <c r="S26" t="str">
+        <v>按级响应</v>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v>A/B级不得由班主任独自处理，必须24-48h内上报学校</v>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
+      </c>
+      <c r="Z26" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA26" t="str">
+        <v>工作手册·附录F（框架参照六力制度）</v>
+      </c>
+      <c r="AB26" t="str">
+        <v>分级处置无遗漏</v>
+      </c>
+      <c r="AC26" t="str">
+        <v>迟报漏报</v>
+      </c>
+      <c r="AD26" t="str">
+        <v>熟悉A-E分级标准</v>
+      </c>
+      <c r="AE26" t="str">
+        <v>A-E点检表、响应动作分级卡</v>
+      </c>
+      <c r="AF26" t="str">
+        <v>A-E响应记录</v>
+      </c>
+      <c r="AG26" t="str">
+        <v/>
+      </c>
+      <c r="AH26" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI26" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CS_RX_26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>危机后班级修复4步</v>
+      </c>
+      <c r="C27" t="str">
+        <v>危机后班级修复4</v>
+      </c>
+      <c r="D27" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E27" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F27" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G27" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H27" t="str">
+        <v>危机处置后的班级二次伤害预防</v>
+      </c>
+      <c r="I27" t="str">
+        <v>high</v>
+      </c>
+      <c r="J27" t="str">
+        <v>CS_AT_09;CS_AT_02</v>
+      </c>
+      <c r="K27" t="str">
+        <v>危机响应迟滞;同伴联结薄弱</v>
+      </c>
+      <c r="L27" t="str">
+        <v>class_system,norm,crisis,relationship,peer</v>
+      </c>
+      <c r="M27" t="str">
+        <v>CS_S1D1</v>
+      </c>
+      <c r="N27" t="str">
+        <v>危机后修复与文化生成，区别于惩罚式处理</v>
+      </c>
+      <c r="O27" t="str">
+        <v>班会复盘（1周内，『我们学到了什么』代替指责）；关系修复（涉及学生+家长1对1，持续4周）；规则审视（1节班会补漏洞）；班主任自我复盘（3天内，复盘卡）</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v>班级二次伤害预防，关系修复完成</v>
+      </c>
+      <c r="R27" t="str">
+        <v>1节班会+1对1</v>
+      </c>
+      <c r="S27" t="str">
+        <v>4周/轮</v>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
+        <v/>
+      </c>
+      <c r="Z27" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA27" t="str">
+        <v>工作手册·第八章8.4</v>
+      </c>
+      <c r="AB27" t="str">
+        <v>复盘完成且班级恢复稳定</v>
+      </c>
+      <c r="AC27" t="str">
+        <v>回避复盘或互相指责</v>
+      </c>
+      <c r="AD27" t="str">
+        <v>准备复盘卡</v>
+      </c>
+      <c r="AE27" t="str">
+        <v>危机处理复盘卡</v>
+      </c>
+      <c r="AF27" t="str">
+        <v>危机处理复盘卡</v>
+      </c>
+      <c r="AG27" t="str">
+        <v/>
+      </c>
+      <c r="AH27" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI27" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CS_RX_27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>绘画投射筛查后处理</v>
+      </c>
+      <c r="C28" t="str">
+        <v>绘画投射筛查后处</v>
+      </c>
+      <c r="D28" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E28" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F28" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G28" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H28" t="str">
+        <v>绘画筛查红旗信号的专业跟进</v>
+      </c>
+      <c r="I28" t="str">
+        <v>high</v>
+      </c>
+      <c r="J28" t="str">
+        <v>CS_AT_09;CS_AT_14</v>
+      </c>
+      <c r="K28" t="str">
+        <v>危机响应迟滞;个体情绪失接</v>
+      </c>
+      <c r="L28" t="str">
+        <v>class_system,norm,crisis,emotion,support</v>
+      </c>
+      <c r="M28" t="str">
+        <v>CS_S1D5;CS_S1D3</v>
+      </c>
+      <c r="N28" t="str">
+        <v>与SDQ、A-E点检构成多源风险识别</v>
+      </c>
+      <c r="O28" t="str">
+        <v>红旗清单判定风险等级（红/橙/黄/绿）；红/橙级转介学校心理专业；保护性因素降级评估；家校沟通协作</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v>红旗信号及时转介，转介及时</v>
+      </c>
+      <c r="R28" t="str">
+        <v>30 分钟</v>
+      </c>
+      <c r="S28" t="str">
+        <v>按需</v>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v>绘画筛查是筛查工具非诊断结论，不得据此给学生贴标签</v>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
+        <v/>
+      </c>
+      <c r="Z28" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA28" t="str">
+        <v>评估库A06对接 / 绘画投射分析参考</v>
+      </c>
+      <c r="AB28" t="str">
+        <v>红/橙级全部转介</v>
+      </c>
+      <c r="AC28" t="str">
+        <v>红旗信号未跟进</v>
+      </c>
+      <c r="AD28" t="str">
+        <v>完成绘画投射筛查</v>
+      </c>
+      <c r="AE28" t="str">
+        <v>绘画筛查指标表、转介沟通话术</v>
+      </c>
+      <c r="AF28" t="str">
+        <v>筛查结论与转介建议</v>
+      </c>
+      <c r="AG28" t="str">
+        <v/>
+      </c>
+      <c r="AH28" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI28" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CS_RX_28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>情绪急救三步法</v>
+      </c>
+      <c r="C29" t="str">
+        <v>情绪急救三步法</v>
+      </c>
+      <c r="D29" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E29" t="str">
+        <v>script</v>
+      </c>
+      <c r="F29" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G29" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H29" t="str">
+        <v>即时情绪崩溃的现场处置</v>
+      </c>
+      <c r="I29" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="J29" t="str">
+        <v>CS_AT_14;CS_AT_09</v>
+      </c>
+      <c r="K29" t="str">
+        <v>个体情绪失接;危机响应迟滞</v>
+      </c>
+      <c r="L29" t="str">
+        <v>class_system,emotion,support,norm,crisis</v>
+      </c>
+      <c r="M29" t="str">
+        <v>CS_S1D5</v>
+      </c>
+      <c r="N29" t="str">
+        <v>危机『即时』层技术，与EQ四步呼应</v>
+      </c>
+      <c r="O29" t="str">
+        <v>停（安全隔开，移除危险源）；听（共情倾听，不评判）；析-选（EQ四步：标情绪-析需求-选行动）</v>
+      </c>
+      <c r="P29" t="str">
+        <v>我听到你现在很（标情绪），你希望（析需求），我们可以（选行动）。</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>现场情绪平复，无升级</v>
+      </c>
+      <c r="R29" t="str">
+        <v>5-10 分钟</v>
+      </c>
+      <c r="S29" t="str">
+        <v>即时</v>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v>周使用超过3次须转介学校心理老师</v>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <v/>
+      </c>
+      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
+        <v/>
+      </c>
+      <c r="Z29" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA29" t="str">
+        <v>技术手册·密码本/EQ</v>
+      </c>
+      <c r="AB29" t="str">
+        <v>现场情绪稳定</v>
+      </c>
+      <c r="AC29" t="str">
+        <v>频繁使用（周&gt;3次）</v>
+      </c>
+      <c r="AD29" t="str">
+        <v>熟记EQ四步</v>
+      </c>
+      <c r="AE29" t="str">
+        <v>情绪急救流程卡、EQ四步海报</v>
+      </c>
+      <c r="AF29" t="str">
+        <v>处置记录</v>
+      </c>
+      <c r="AG29" t="str">
+        <v/>
+      </c>
+      <c r="AH29" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI29" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CS_RX_29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>家校沟通SOP</v>
+      </c>
+      <c r="C30" t="str">
+        <v>家校沟通SOP</v>
+      </c>
+      <c r="D30" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E30" t="str">
+        <v>script</v>
+      </c>
+      <c r="F30" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G30" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H30" t="str">
+        <v>家长日常反馈与投诉处理</v>
+      </c>
+      <c r="I30" t="str">
+        <v>low</v>
+      </c>
+      <c r="J30" t="str">
+        <v>CS_AT_03</v>
+      </c>
+      <c r="K30" t="str">
+        <v>家校连接松散</v>
+      </c>
+      <c r="L30" t="str">
+        <v>class_system,relationship,family</v>
+      </c>
+      <c r="M30" t="str">
+        <v>CS_S1D1</v>
+      </c>
+      <c r="N30" t="str">
+        <v>三通工程+73855法则配套使用</v>
+      </c>
+      <c r="O30" t="str">
+        <v>日常反馈（73855：70%积极+30%待改进）；投诉处理（先跟后带+意义换框）；结构化表达（事实-影响-建议）</v>
+      </c>
+      <c r="P30" t="str">
+        <v>先说事实，再说影响，最后给建议；积极与待改进保持70:30。</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>关键通知响应率≥85%</v>
+      </c>
+      <c r="R30" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S30" t="str">
+        <v>每周1次反馈</v>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <v/>
+      </c>
+      <c r="X30" t="str">
+        <v/>
+      </c>
+      <c r="Y30" t="str">
+        <v/>
+      </c>
+      <c r="Z30" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA30" t="str">
+        <v>工作手册·第七章7.4 / 技术手册·第十八部分</v>
+      </c>
+      <c r="AB30" t="str">
+        <v>家长群响应率提升</v>
+      </c>
+      <c r="AC30" t="str">
+        <v>沟通单向无回执</v>
+      </c>
+      <c r="AD30" t="str">
+        <v>熟悉73855法则</v>
+      </c>
+      <c r="AE30" t="str">
+        <v>73855沟通法则、分场景话术库</v>
+      </c>
+      <c r="AF30" t="str">
+        <v>沟通记录</v>
+      </c>
+      <c r="AG30" t="str">
+        <v/>
+      </c>
+      <c r="AH30" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI30" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CS_RX_30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>家长会4种形式</v>
+      </c>
+      <c r="C31" t="str">
+        <v>家长会4种形式</v>
+      </c>
+      <c r="D31" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E31" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F31" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G31" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H31" t="str">
+        <v>家长会设计与实施</v>
+      </c>
+      <c r="I31" t="str">
+        <v>low</v>
+      </c>
+      <c r="J31" t="str">
+        <v>CS_AT_03</v>
+      </c>
+      <c r="K31" t="str">
+        <v>家校连接松散</v>
+      </c>
+      <c r="L31" t="str">
+        <v>class_system,relationship,family</v>
+      </c>
+      <c r="M31" t="str">
+        <v>CS_S1D1</v>
+      </c>
+      <c r="N31" t="str">
+        <v>把家长会从通报会变成共同叙事场</v>
+      </c>
+      <c r="O31" t="str">
+        <v>从『情况通报』升级为『共同叙事』；4形式（全体/小组/工作坊/学生主导）；先展示非学业成就再谈学业</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v>家长参与度提升，参与门槛降低</v>
+      </c>
+      <c r="R31" t="str">
+        <v>1-2 小时</v>
+      </c>
+      <c r="S31" t="str">
+        <v>每学期1-2次</v>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+      <c r="U31" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V31" t="str">
+        <v/>
+      </c>
+      <c r="W31" t="str">
+        <v/>
+      </c>
+      <c r="X31" t="str">
+        <v/>
+      </c>
+      <c r="Y31" t="str">
+        <v/>
+      </c>
+      <c r="Z31" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA31" t="str">
+        <v>工作手册·第七章7.3</v>
+      </c>
+      <c r="AB31" t="str">
+        <v>家长到场率提升</v>
+      </c>
+      <c r="AC31" t="str">
+        <v>流于情况通报</v>
+      </c>
+      <c r="AD31" t="str">
+        <v>选择家长会形式</v>
+      </c>
+      <c r="AE31" t="str">
+        <v>家长会形式选择表、共同叙事模板</v>
+      </c>
+      <c r="AF31" t="str">
+        <v>家长会方案</v>
+      </c>
+      <c r="AG31" t="str">
+        <v/>
+      </c>
+      <c r="AH31" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI31" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CS_RX_31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>家访与家长工作坊</v>
+      </c>
+      <c r="C32" t="str">
+        <v>家访与家长工作坊</v>
+      </c>
+      <c r="D32" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="E32" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F32" t="str">
+        <v>primary</v>
+      </c>
+      <c r="G32" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H32" t="str">
+        <v>深度协同、降低参与门槛</v>
+      </c>
+      <c r="I32" t="str">
+        <v>low</v>
+      </c>
+      <c r="J32" t="str">
+        <v>CS_AT_03</v>
+      </c>
+      <c r="K32" t="str">
+        <v>家校连接松散</v>
+      </c>
+      <c r="L32" t="str">
+        <v>class_system,relationship,family</v>
+      </c>
+      <c r="M32" t="str">
+        <v>CS_S1D1</v>
+      </c>
+      <c r="N32" t="str">
+        <v>降低参与门槛让家校连接持续发生</v>
+      </c>
+      <c r="O32" t="str">
+        <v>个别家访（针对需额外支持学生）；家长工作坊（每学期1次主题技能）；降低门槛（把『参会』改为『群里回个表情』）</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v>家访覆盖率提升，家校深度协同</v>
+      </c>
+      <c r="R32" t="str">
+        <v>家访30分钟</v>
+      </c>
+      <c r="S32" t="str">
+        <v>每学期1次工作坊</v>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+      <c r="U32" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V32" t="str">
+        <v/>
+      </c>
+      <c r="W32" t="str">
+        <v/>
+      </c>
+      <c r="X32" t="str">
+        <v/>
+      </c>
+      <c r="Y32" t="str">
+        <v/>
+      </c>
+      <c r="Z32" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA32" t="str">
+        <v>工作手册/技术手册·家校共育</v>
+      </c>
+      <c r="AB32" t="str">
+        <v>家访完成率提升</v>
+      </c>
+      <c r="AC32" t="str">
+        <v>家长拒绝沟通</v>
+      </c>
+      <c r="AD32" t="str">
+        <v>制定家访提纲</v>
+      </c>
+      <c r="AE32" t="str">
+        <v>家访提纲、工作坊方案模板</v>
+      </c>
+      <c r="AF32" t="str">
+        <v>家访记录</v>
+      </c>
+      <c r="AG32" t="str">
+        <v/>
+      </c>
+      <c r="AH32" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AI32" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ32" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ32"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1222,10 +3972,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>和学生一起用一句话说清本学期班级要成为什么样</v>
+        <v>发放五系统自评表（15题，1-5分）</v>
       </c>
       <c r="D2" t="str">
-        <v>和学生一起用一句话说清本学期班级要成为什么样</v>
+        <v>发放五系统自评表（15题，1-5分）</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -1234,13 +3984,13 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>我们这学期只做好一件事，你们觉得应该是哪一件？</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -1254,10 +4004,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>把这句话拆成三个可观察的里程碑</v>
+        <v>加总得15-75分</v>
       </c>
       <c r="D3" t="str">
-        <v>把这句话拆成三个可观察的里程碑</v>
+        <v>加总得15-75分</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -1272,7 +4022,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -1286,10 +4036,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>为第一个里程碑写清完成标准和检查时间</v>
+        <v>四档解读：60-75健康 / 45-59关注 /</v>
       </c>
       <c r="D4" t="str">
-        <v>为第一个里程碑写清完成标准和检查时间</v>
+        <v>四档解读：60-75健康 / 45-59关注 / 30-44系统问题 / &lt;30立即介入</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -1304,7 +4054,7 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1318,10 +4068,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>贴在教室并每两周对照一次</v>
+        <v>按短板系统匹配对应模块工具</v>
       </c>
       <c r="D5" t="str">
-        <v>贴在教室并每两周对照一次</v>
+        <v>按短板系统匹配对应模块工具</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -1336,7 +4086,7 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1350,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>选一个每天都发生的事务（如晨检、放学清扫）</v>
+        <v>识别4种截断（积累/堵塞/溃堤/重建）</v>
       </c>
       <c r="D6" t="str">
-        <v>选一个每天都发生的事务（如晨检、放学清扫）</v>
+        <v>识别4种截断（积累/堵塞/溃堤/重建）</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -1362,13 +4112,13 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>这件事从明天起由你负责，遇到处理不了的情况再来找我。</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1382,10 +4132,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>写清责任人、执行步骤、异常处理和复盘时间</v>
+        <v>疏浚SOP·定期排空：班会复盘</v>
       </c>
       <c r="D7" t="str">
-        <v>写清责任人、执行步骤、异常处理和复盘时间</v>
+        <v>疏浚SOP·定期排空：班会复盘</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -1400,7 +4150,7 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -1414,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>让学生试运行三天，教师只观察不介入</v>
+        <v>疏浚SOP·拓宽河道：声音通道</v>
       </c>
       <c r="D8" t="str">
-        <v>让学生试运行三天，教师只观察不介入</v>
+        <v>疏浚SOP·拓宽河道：声音通道</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1432,7 +4182,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1446,10 +4196,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>第四天复盘，只调整卡住的那一步</v>
+        <v>疏浚SOP·降低水位：小步成功</v>
       </c>
       <c r="D9" t="str">
-        <v>第四天复盘，只调整卡住的那一步</v>
+        <v>疏浚SOP·降低水位：小步成功</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -1464,7 +4214,7 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -1472,16 +4222,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CS_RX_03</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="B10" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" t="str">
-        <v>活动结束当天，留出十分钟</v>
+        <v>溃堤预警：出现集体辞职/安全事件立即启动危机响应</v>
       </c>
       <c r="D10" t="str">
-        <v>活动结束当天，留出十分钟</v>
+        <v>溃堤预警：出现集体辞职/安全事件立即启动危机响应</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1490,13 +4240,13 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>今天我们只讨论一件事：哪个环节帮助大家更稳定，哪个环节明天需要调整。</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1507,13 +4257,13 @@
         <v>CS_RX_03</v>
       </c>
       <c r="B11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>每人说一个「下次要保留的动作」</v>
+        <v>判能力（会不会）</v>
       </c>
       <c r="D11" t="str">
-        <v>每人说一个「下次要保留的动作」</v>
+        <v>判能力（会不会）</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1528,7 +4278,7 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1539,13 +4289,13 @@
         <v>CS_RX_03</v>
       </c>
       <c r="B12" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="str">
-        <v>每人说一个「下次要调整的动作」</v>
+        <v>判意愿（想不想）</v>
       </c>
       <c r="D12" t="str">
-        <v>每人说一个「下次要调整的动作」</v>
+        <v>判意愿（想不想）</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -1560,7 +4310,7 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1571,13 +4321,13 @@
         <v>CS_RX_03</v>
       </c>
       <c r="B13" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="str">
-        <v>教师只记录不评价，把结果贴在班级角</v>
+        <v>定四型（成功/挫折/对抗/放弃）</v>
       </c>
       <c r="D13" t="str">
-        <v>教师只记录不评价，把结果贴在班级角</v>
+        <v>定四型（成功/挫折/对抗/放弃）</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -1592,7 +4342,7 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1600,16 +4350,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_03</v>
       </c>
       <c r="B14" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C14" t="str">
-        <v>挑一条最常被违反的规则</v>
+        <v>匹配策略（赋能/拆解/连接/降门槛）</v>
       </c>
       <c r="D14" t="str">
-        <v>挑一条最常被违反的规则</v>
+        <v>匹配策略（赋能/拆解/连接/降门槛）</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -1618,13 +4368,13 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>这条规则不是为了限制大家，而是为了让学习和相处更可预期。我们先试行三天再复盘。</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1635,13 +4385,13 @@
         <v>CS_RX_04</v>
       </c>
       <c r="B15" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="str">
-        <v>让学生说出这条规则存在的理由，教师补充缺失的部分</v>
+        <v>岗位发布（开学前张贴，1-2年师生共议，3-6年</v>
       </c>
       <c r="D15" t="str">
-        <v>让学生说出这条规则存在的理由，教师补充缺失的部分</v>
+        <v>岗位发布（开学前张贴，1-2年师生共议，3-6年自主申报）</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -1656,7 +4406,7 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1667,13 +4417,13 @@
         <v>CS_RX_04</v>
       </c>
       <c r="B16" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="str">
-        <v>一起把规则改写成可观察的行为描述</v>
+        <v>自主报名</v>
       </c>
       <c r="D16" t="str">
-        <v>一起把规则改写成可观察的行为描述</v>
+        <v>自主报名</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1688,7 +4438,7 @@
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1699,13 +4449,13 @@
         <v>CS_RX_04</v>
       </c>
       <c r="B17" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="str">
-        <v>约定试行两周后复盘</v>
+        <v>岗位答辩（1-2分钟说想做+怎么做）</v>
       </c>
       <c r="D17" t="str">
-        <v>约定试行两周后复盘</v>
+        <v>岗位答辩（1-2分钟说想做+怎么做）</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1720,7 +4470,7 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1728,16 +4478,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B18" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="str">
-        <v>分开双方，各自说清「发生了什么」，只说事实</v>
+        <v>试用考核（1周）</v>
       </c>
       <c r="D18" t="str">
-        <v>分开双方，各自说清「发生了什么」，只说事实</v>
+        <v>试用考核（1周）</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1746,13 +4496,13 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>我们先不讨论谁对谁错，先把事实说清楚。</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1760,16 +4510,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B19" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="str">
-        <v>各自说「我当时的感受」，不评价对方</v>
+        <v>正式任命</v>
       </c>
       <c r="D19" t="str">
-        <v>各自说「我当时的感受」，不评价对方</v>
+        <v>正式任命</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1784,7 +4534,7 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1792,16 +4542,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="B20" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C20" t="str">
-        <v>各自说「我希望接下来怎样」</v>
+        <v>月度培训赋能（8课时例会）</v>
       </c>
       <c r="D20" t="str">
-        <v>各自说「我希望接下来怎样」</v>
+        <v>月度培训赋能（8课时例会）</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1816,7 +4566,7 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1827,13 +4577,13 @@
         <v>CS_RX_05</v>
       </c>
       <c r="B21" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" t="str">
-        <v>共同确认一个可执行的下一步，并约定检查时间</v>
+        <v>案例收集</v>
       </c>
       <c r="D21" t="str">
-        <v>共同确认一个可执行的下一步，并约定检查时间</v>
+        <v>案例收集</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1848,7 +4598,7 @@
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1856,16 +4606,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B22" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v>按学习和性格互补原则做两两配对</v>
+        <v>小组讨论</v>
       </c>
       <c r="D22" t="str">
-        <v>按学习和性格互补原则做两两配对</v>
+        <v>小组讨论</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1874,13 +4624,13 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>你们两个这周互相提醒一下，周五我来听听你们互相帮到了什么。</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1888,16 +4638,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B23" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="str">
-        <v>给每对一个具体的互助任务，如每天互查作业</v>
+        <v>全班共商</v>
       </c>
       <c r="D23" t="str">
-        <v>给每对一个具体的互助任务，如每天互查作业</v>
+        <v>全班共商</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1912,7 +4662,7 @@
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1920,16 +4670,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="B24" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="str">
-        <v>每周收一次简短反馈，只问「这周互相帮到了什么」</v>
+        <v>草拟公约（8-12条）</v>
       </c>
       <c r="D24" t="str">
-        <v>每周收一次简短反馈，只问「这周互相帮到了什么」</v>
+        <v>草拟公约（8-12条）</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1944,7 +4694,7 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1952,46 +4702,3182 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>CS_RX_05</v>
+      </c>
+      <c r="B25" t="str">
+        <v>5</v>
+      </c>
+      <c r="C25" t="str">
+        <v>签字上墙（师生签字）</v>
+      </c>
+      <c r="D25" t="str">
+        <v>签字上墙（师生签字）</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_RX_05</v>
+      </c>
+      <c r="B26" t="str">
+        <v>6</v>
+      </c>
+      <c r="C26" t="str">
+        <v>执行评估（定期修订）</v>
+      </c>
+      <c r="D26" t="str">
+        <v>执行评估（定期修订）</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v>CS_RX_06</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B27" t="str">
+        <v>1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>分开冷静</v>
+      </c>
+      <c r="D27" t="str">
+        <v>分开冷静</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CS_RX_06</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>各自陈述（事实-影响-感受）</v>
+      </c>
+      <c r="D28" t="str">
+        <v>各自陈述（事实-影响-感受）</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CS_RX_06</v>
+      </c>
+      <c r="B29" t="str">
+        <v>3</v>
+      </c>
+      <c r="C29" t="str">
+        <v>修复性对话（你做了什么/影响了谁/怎么修复）</v>
+      </c>
+      <c r="D29" t="str">
+        <v>修复性对话（你做了什么/影响了谁/怎么修复）</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CS_RX_06</v>
+      </c>
+      <c r="B30" t="str">
         <v>4</v>
       </c>
-      <c r="C25" t="str">
-        <v>两周后按反馈调整配对</v>
-      </c>
-      <c r="D25" t="str">
-        <v>两周后按反馈调整配对</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v>完成本步骤描述的动作</v>
-      </c>
-      <c r="J25" t="str">
+      <c r="C30" t="str">
+        <v>达成修复约定</v>
+      </c>
+      <c r="D30" t="str">
+        <v>达成修复约定</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CS_RX_06</v>
+      </c>
+      <c r="B31" t="str">
+        <v>5</v>
+      </c>
+      <c r="C31" t="str">
+        <v>跟进复盘</v>
+      </c>
+      <c r="D31" t="str">
+        <v>跟进复盘</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="B32" t="str">
+        <v>1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>73855法则（7%文字/38%语调/55%肢体</v>
+      </c>
+      <c r="D32" t="str">
+        <v>73855法则（7%文字/38%语调/55%肢体，70%积极+30%待改进）</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2</v>
+      </c>
+      <c r="C33" t="str">
+        <v>意义换框（把『下滑』重构为『成长课题』）</v>
+      </c>
+      <c r="D33" t="str">
+        <v>意义换框（把『下滑』重构为『成长课题』）</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="B34" t="str">
+        <v>3</v>
+      </c>
+      <c r="C34" t="str">
+        <v>EQ四步（停-听-标-析-选）</v>
+      </c>
+      <c r="D34" t="str">
+        <v>EQ四步（停-听-标-析-选）</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="B35" t="str">
+        <v>1</v>
+      </c>
+      <c r="C35" t="str">
+        <v>安全型：维持安全基地</v>
+      </c>
+      <c r="D35" t="str">
+        <v>安全型：维持安全基地</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2</v>
+      </c>
+      <c r="C36" t="str">
+        <v>A型（回避）：主动靠近+低压力邀请</v>
+      </c>
+      <c r="D36" t="str">
+        <v>A型（回避）：主动靠近+低压力邀请</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="B37" t="str">
+        <v>3</v>
+      </c>
+      <c r="C37" t="str">
+        <v>B型（焦虑）：可预测回应+稳定陪伴</v>
+      </c>
+      <c r="D37" t="str">
+        <v>B型（焦虑）：可预测回应+稳定陪伴</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="B38" t="str">
+        <v>4</v>
+      </c>
+      <c r="C38" t="str">
+        <v>C型（抗拒）：先连接情绪再提要求</v>
+      </c>
+      <c r="D38" t="str">
+        <v>C型（抗拒）：先连接情绪再提要求</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="B39" t="str">
+        <v>5</v>
+      </c>
+      <c r="C39" t="str">
+        <v>D型（混乱）：优先建安全感，1个工作日内转介心理</v>
+      </c>
+      <c r="D39" t="str">
+        <v>D型（混乱）：优先建安全感，1个工作日内转介心理专业</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>CS_RX_09</v>
+      </c>
+      <c r="B40" t="str">
+        <v>1</v>
+      </c>
+      <c r="C40" t="str">
+        <v>周仪式（晨圈/点赞）</v>
+      </c>
+      <c r="D40" t="str">
+        <v>周仪式（晨圈/点赞）</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>CS_RX_09</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2</v>
+      </c>
+      <c r="C41" t="str">
+        <v>月度团建</v>
+      </c>
+      <c r="D41" t="str">
+        <v>月度团建</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>CS_RX_09</v>
+      </c>
+      <c r="B42" t="str">
+        <v>3</v>
+      </c>
+      <c r="C42" t="str">
+        <v>混搭座位+小组任务</v>
+      </c>
+      <c r="D42" t="str">
+        <v>混搭座位+小组任务</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>CS_RX_09</v>
+      </c>
+      <c r="B43" t="str">
+        <v>4</v>
+      </c>
+      <c r="C43" t="str">
+        <v>夸夸墙</v>
+      </c>
+      <c r="D43" t="str">
+        <v>夸夸墙</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>CS_RX_10</v>
+      </c>
+      <c r="B44" t="str">
+        <v>1</v>
+      </c>
+      <c r="C44" t="str">
+        <v>1个大管家（班委）+1个小管家（全班轮值）</v>
+      </c>
+      <c r="D44" t="str">
+        <v>1个大管家（班委）+1个小管家（全班轮值）</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>CS_RX_10</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2</v>
+      </c>
+      <c r="C45" t="str">
+        <v>2个长期岗位+2个短期项目</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2个长期岗位+2个短期项目</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>CS_RX_10</v>
+      </c>
+      <c r="B46" t="str">
+        <v>3</v>
+      </c>
+      <c r="C46" t="str">
+        <v>区块长制（人人有事做，事事有人管）</v>
+      </c>
+      <c r="D46" t="str">
+        <v>区块长制（人人有事做，事事有人管）</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>CS_RX_11</v>
+      </c>
+      <c r="B47" t="str">
+        <v>1</v>
+      </c>
+      <c r="C47" t="str">
+        <v>长期岗学期初选，稳定运行</v>
+      </c>
+      <c r="D47" t="str">
+        <v>长期岗学期初选，稳定运行</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>CS_RX_11</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2</v>
+      </c>
+      <c r="C48" t="str">
+        <v>短期项目按需发布</v>
+      </c>
+      <c r="D48" t="str">
+        <v>短期项目按需发布</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>CS_RX_11</v>
+      </c>
+      <c r="B49" t="str">
+        <v>3</v>
+      </c>
+      <c r="C49" t="str">
+        <v>轮值制让每人有机会</v>
+      </c>
+      <c r="D49" t="str">
+        <v>轮值制让每人有机会</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>CS_RX_11</v>
+      </c>
+      <c r="B50" t="str">
+        <v>4</v>
+      </c>
+      <c r="C50" t="str">
+        <v>每月扩展1项新责任</v>
+      </c>
+      <c r="D50" t="str">
+        <v>每月扩展1项新责任</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>CS_RX_12</v>
+      </c>
+      <c r="B51" t="str">
+        <v>1</v>
+      </c>
+      <c r="C51" t="str">
+        <v>明确原则（身高+视力+男女混搭+性格互补+小组合</v>
+      </c>
+      <c r="D51" t="str">
+        <v>明确原则（身高+视力+男女混搭+性格互补+小组合作便利）</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>CS_RX_12</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2</v>
+      </c>
+      <c r="C52" t="str">
+        <v>拟方案→班级共商→确定</v>
+      </c>
+      <c r="D52" t="str">
+        <v>拟方案→班级共商→确定</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>CS_RX_12</v>
+      </c>
+      <c r="B53" t="str">
+        <v>3</v>
+      </c>
+      <c r="C53" t="str">
+        <v>自评座位满意度</v>
+      </c>
+      <c r="D53" t="str">
+        <v>自评座位满意度</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>CS_RX_12</v>
+      </c>
+      <c r="B54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C54" t="str">
+        <v>每学期调整1-2次</v>
+      </c>
+      <c r="D54" t="str">
+        <v>每学期调整1-2次</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>CS_RX_13</v>
+      </c>
+      <c r="B55" t="str">
+        <v>1</v>
+      </c>
+      <c r="C55" t="str">
+        <v>时钟伙伴（12/3/6/9点找不同伙伴，自然打破</v>
+      </c>
+      <c r="D55" t="str">
+        <v>时钟伙伴（12/3/6/9点找不同伙伴，自然打破小团体）</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>CS_RX_13</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2</v>
+      </c>
+      <c r="C56" t="str">
+        <v>PIES原则（正向互赖/个体责任/平等参与/同时</v>
+      </c>
+      <c r="D56" t="str">
+        <v>PIES原则（正向互赖/个体责任/平等参与/同时互动）</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>CS_RX_13</v>
+      </c>
+      <c r="B57" t="str">
+        <v>3</v>
+      </c>
+      <c r="C57" t="str">
+        <v>从1分钟逐步加长</v>
+      </c>
+      <c r="D57" t="str">
+        <v>从1分钟逐步加长</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>CS_RX_14</v>
+      </c>
+      <c r="B58" t="str">
+        <v>1</v>
+      </c>
+      <c r="C58" t="str">
+        <v>共识复盘（每月）</v>
+      </c>
+      <c r="D58" t="str">
+        <v>共识复盘（每月）</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>CS_RX_14</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2</v>
+      </c>
+      <c r="C59" t="str">
+        <v>执行评估（达标/修订）</v>
+      </c>
+      <c r="D59" t="str">
+        <v>执行评估（达标/修订）</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>CS_RX_14</v>
+      </c>
+      <c r="B60" t="str">
+        <v>3</v>
+      </c>
+      <c r="C60" t="str">
+        <v>配套五星点检</v>
+      </c>
+      <c r="D60" t="str">
+        <v>配套五星点检</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>CS_RX_14</v>
+      </c>
+      <c r="B61" t="str">
+        <v>4</v>
+      </c>
+      <c r="C61" t="str">
+        <v>修订启动（制度自转期）</v>
+      </c>
+      <c r="D61" t="str">
+        <v>修订启动（制度自转期）</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>CS_RX_15</v>
+      </c>
+      <c r="B62" t="str">
+        <v>1</v>
+      </c>
+      <c r="C62" t="str">
+        <v>日点检（班委/值日班长）</v>
+      </c>
+      <c r="D62" t="str">
+        <v>日点检（班委/值日班长）</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>CS_RX_15</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2</v>
+      </c>
+      <c r="C63" t="str">
+        <v>周点检（班主任）</v>
+      </c>
+      <c r="D63" t="str">
+        <v>周点检（班主任）</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>CS_RX_15</v>
+      </c>
+      <c r="B64" t="str">
+        <v>3</v>
+      </c>
+      <c r="C64" t="str">
+        <v>月反馈（家长/五星）</v>
+      </c>
+      <c r="D64" t="str">
+        <v>月反馈（家长/五星）</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>CS_RX_15</v>
+      </c>
+      <c r="B65" t="str">
+        <v>4</v>
+      </c>
+      <c r="C65" t="str">
+        <v>三级网络覆盖五维度</v>
+      </c>
+      <c r="D65" t="str">
+        <v>三级网络覆盖五维度</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>CS_RX_16</v>
+      </c>
+      <c r="B66" t="str">
+        <v>1</v>
+      </c>
+      <c r="C66" t="str">
+        <v>德育常规1-5星</v>
+      </c>
+      <c r="D66" t="str">
+        <v>德育常规1-5星</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>CS_RX_16</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2</v>
+      </c>
+      <c r="C67" t="str">
+        <v>学风管理1-5星</v>
+      </c>
+      <c r="D67" t="str">
+        <v>学风管理1-5星</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>CS_RX_16</v>
+      </c>
+      <c r="B68" t="str">
+        <v>3</v>
+      </c>
+      <c r="C68" t="str">
+        <v>家校共育1-5星</v>
+      </c>
+      <c r="D68" t="str">
+        <v>家校共育1-5星</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>CS_RX_16</v>
+      </c>
+      <c r="B69" t="str">
+        <v>4</v>
+      </c>
+      <c r="C69" t="str">
+        <v>班主任为第一责任人</v>
+      </c>
+      <c r="D69" t="str">
+        <v>班主任为第一责任人</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>CS_RX_16</v>
+      </c>
+      <c r="B70" t="str">
+        <v>5</v>
+      </c>
+      <c r="C70" t="str">
+        <v>月度评定，9/12/15星→三/四/五星班级</v>
+      </c>
+      <c r="D70" t="str">
+        <v>月度评定，9/12/15星→三/四/五星班级</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>CS_RX_17</v>
+      </c>
+      <c r="B71" t="str">
+        <v>1</v>
+      </c>
+      <c r="C71" t="str">
+        <v>「三个1分钟」（课前组织/课中每15分钟巡视/课</v>
+      </c>
+      <c r="D71" t="str">
+        <v>「三个1分钟」（课前组织/课中每15分钟巡视/课后小结）</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>CS_RX_17</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2</v>
+      </c>
+      <c r="C72" t="str">
+        <v>早读-课间-眼保健操-午餐-放学节点</v>
+      </c>
+      <c r="D72" t="str">
+        <v>早读-课间-眼保健操-午餐-放学节点</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>CS_RX_17</v>
+      </c>
+      <c r="B73" t="str">
+        <v>3</v>
+      </c>
+      <c r="C73" t="str">
+        <v>周班会（班委主舞台，班主任导演）</v>
+      </c>
+      <c r="D73" t="str">
+        <v>周班会（班委主舞台，班主任导演）</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>CS_RX_18</v>
+      </c>
+      <c r="B74" t="str">
+        <v>1</v>
+      </c>
+      <c r="C74" t="str">
+        <v>师生共议『班级想要的样子』</v>
+      </c>
+      <c r="D74" t="str">
+        <v>师生共议『班级想要的样子』</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>CS_RX_18</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2</v>
+      </c>
+      <c r="C75" t="str">
+        <v>凝练班名/口号/班级目标</v>
+      </c>
+      <c r="D75" t="str">
+        <v>凝练班名/口号/班级目标</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>CS_RX_18</v>
+      </c>
+      <c r="B76" t="str">
+        <v>3</v>
+      </c>
+      <c r="C76" t="str">
+        <v>上墙可视化</v>
+      </c>
+      <c r="D76" t="str">
+        <v>上墙可视化</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>CS_RX_19</v>
+      </c>
+      <c r="B77" t="str">
+        <v>1</v>
+      </c>
+      <c r="C77" t="str">
+        <v>学期初设个人目标卡</v>
+      </c>
+      <c r="D77" t="str">
+        <v>学期初设个人目标卡</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>CS_RX_19</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2</v>
+      </c>
+      <c r="C78" t="str">
+        <v>过程记录（档案袋：文字+数据+反思）</v>
+      </c>
+      <c r="D78" t="str">
+        <v>过程记录（档案袋：文字+数据+反思）</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>CS_RX_19</v>
+      </c>
+      <c r="B79" t="str">
+        <v>3</v>
+      </c>
+      <c r="C79" t="str">
+        <v>家长会/展示日呈现</v>
+      </c>
+      <c r="D79" t="str">
+        <v>家长会/展示日呈现</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>CS_RX_20</v>
+      </c>
+      <c r="B80" t="str">
+        <v>1</v>
+      </c>
+      <c r="C80" t="str">
+        <v>目标墙张贴</v>
+      </c>
+      <c r="D80" t="str">
+        <v>目标墙张贴</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>CS_RX_20</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2</v>
+      </c>
+      <c r="C81" t="str">
+        <v>进度贴纸标记</v>
+      </c>
+      <c r="D81" t="str">
+        <v>进度贴纸标记</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>CS_RX_20</v>
+      </c>
+      <c r="B82" t="str">
+        <v>3</v>
+      </c>
+      <c r="C82" t="str">
+        <v>月度复盘会</v>
+      </c>
+      <c r="D82" t="str">
+        <v>月度复盘会</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>CS_RX_21</v>
+      </c>
+      <c r="B83" t="str">
+        <v>1</v>
+      </c>
+      <c r="C83" t="str">
+        <v>设安全角（软垫/绘本/情绪卡）</v>
+      </c>
+      <c r="D83" t="str">
+        <v>设安全角（软垫/绘本/情绪卡）</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>CS_RX_21</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2</v>
+      </c>
+      <c r="C84" t="str">
+        <v>建安全信号（举手求助）</v>
+      </c>
+      <c r="D84" t="str">
+        <v>建安全信号（举手求助）</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>CS_RX_21</v>
+      </c>
+      <c r="B85" t="str">
+        <v>3</v>
+      </c>
+      <c r="C85" t="str">
+        <v>允许短暂休息但明确『休息后回来继续』</v>
+      </c>
+      <c r="D85" t="str">
+        <v>允许短暂休息但明确『休息后回来继续』</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>CS_RX_21</v>
+      </c>
+      <c r="B86" t="str">
+        <v>4</v>
+      </c>
+      <c r="C86" t="str">
+        <v>频率过高（周&gt;3次）转介心理</v>
+      </c>
+      <c r="D86" t="str">
+        <v>频率过高（周&gt;3次）转介心理</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>CS_RX_22</v>
+      </c>
+      <c r="B87" t="str">
+        <v>1</v>
+      </c>
+      <c r="C87" t="str">
+        <v>葡萄干练习（30秒观察一颗）</v>
+      </c>
+      <c r="D87" t="str">
+        <v>葡萄干练习（30秒观察一颗）</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>CS_RX_22</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2</v>
+      </c>
+      <c r="C88" t="str">
+        <v>呼吸计时器（3分钟『大脑充电器』）</v>
+      </c>
+      <c r="D88" t="str">
+        <v>呼吸计时器（3分钟『大脑充电器』）</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>CS_RX_22</v>
+      </c>
+      <c r="B89" t="str">
+        <v>3</v>
+      </c>
+      <c r="C89" t="str">
+        <v>时段表（晨间/课前/午后）</v>
+      </c>
+      <c r="D89" t="str">
+        <v>时段表（晨间/课前/午后）</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>CS_RX_22</v>
+      </c>
+      <c r="B90" t="str">
+        <v>4</v>
+      </c>
+      <c r="C90" t="str">
+        <v>从1分钟逐步加到3分钟</v>
+      </c>
+      <c r="D90" t="str">
+        <v>从1分钟逐步加到3分钟</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>CS_RX_23</v>
+      </c>
+      <c r="B91" t="str">
+        <v>1</v>
+      </c>
+      <c r="C91" t="str">
+        <v>6项小学重点（创造力/勇敢/仁爱/公平/领导力/</v>
+      </c>
+      <c r="D91" t="str">
+        <v>6项小学重点（创造力/勇敢/仁爱/公平/领导力/好奇）</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>CS_RX_23</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2</v>
+      </c>
+      <c r="C92" t="str">
+        <v>12项优势卡</v>
+      </c>
+      <c r="D92" t="str">
+        <v>12项优势卡</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>CS_RX_23</v>
+      </c>
+      <c r="B93" t="str">
+        <v>3</v>
+      </c>
+      <c r="C93" t="str">
+        <v>发现-命名-强化话术</v>
+      </c>
+      <c r="D93" t="str">
+        <v>发现-命名-强化话术</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>CS_RX_23</v>
+      </c>
+      <c r="B94" t="str">
+        <v>4</v>
+      </c>
+      <c r="C94" t="str">
+        <v>学科渗透（语文渗善良/数学渗坚持）</v>
+      </c>
+      <c r="D94" t="str">
+        <v>学科渗透（语文渗善良/数学渗坚持）</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>CS_RX_24</v>
+      </c>
+      <c r="B95" t="str">
+        <v>1</v>
+      </c>
+      <c r="C95" t="str">
+        <v>每日点赞</v>
+      </c>
+      <c r="D95" t="str">
+        <v>每日点赞</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>CS_RX_24</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2</v>
+      </c>
+      <c r="C96" t="str">
+        <v>夸夸墙</v>
+      </c>
+      <c r="D96" t="str">
+        <v>夸夸墙</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>CS_RX_24</v>
+      </c>
+      <c r="B97" t="str">
+        <v>3</v>
+      </c>
+      <c r="C97" t="str">
+        <v>发现-命名-强化话术</v>
+      </c>
+      <c r="D97" t="str">
+        <v>发现-命名-强化话术</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B98" t="str">
+        <v>1</v>
+      </c>
+      <c r="C98" t="str">
+        <v>A级（安全事件）即时处置</v>
+      </c>
+      <c r="D98" t="str">
+        <v>A级（安全事件）即时处置</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2</v>
+      </c>
+      <c r="C99" t="str">
+        <v>B级（高风险：欺凌/自伤）2h内班主任+心理+家</v>
+      </c>
+      <c r="D99" t="str">
+        <v>B级（高风险：欺凌/自伤）2h内班主任+心理+家长</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B100" t="str">
+        <v>3</v>
+      </c>
+      <c r="C100" t="str">
+        <v>C级（中度）1周约谈+班级支持</v>
+      </c>
+      <c r="D100" t="str">
+        <v>C级（中度）1周约谈+班级支持</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B101" t="str">
+        <v>4</v>
+      </c>
+      <c r="C101" t="str">
+        <v>D级（轻度）1月家校沟通</v>
+      </c>
+      <c r="D101" t="str">
+        <v>D级（轻度）1月家校沟通</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B102" t="str">
+        <v>5</v>
+      </c>
+      <c r="C102" t="str">
+        <v>E级（健康）月度追踪</v>
+      </c>
+      <c r="D102" t="str">
+        <v>E级（健康）月度追踪</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B103" t="str">
+        <v>6</v>
+      </c>
+      <c r="C103" t="str">
+        <v>A/B级24-48h上报</v>
+      </c>
+      <c r="D103" t="str">
+        <v>A/B级24-48h上报</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>CS_RX_26</v>
+      </c>
+      <c r="B104" t="str">
+        <v>1</v>
+      </c>
+      <c r="C104" t="str">
+        <v>班会复盘（1周内，『我们学到了什么』代替指责）</v>
+      </c>
+      <c r="D104" t="str">
+        <v>班会复盘（1周内，『我们学到了什么』代替指责）</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>CS_RX_26</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2</v>
+      </c>
+      <c r="C105" t="str">
+        <v>关系修复（涉及学生+家长1对1，持续4周）</v>
+      </c>
+      <c r="D105" t="str">
+        <v>关系修复（涉及学生+家长1对1，持续4周）</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>CS_RX_26</v>
+      </c>
+      <c r="B106" t="str">
+        <v>3</v>
+      </c>
+      <c r="C106" t="str">
+        <v>规则审视（1节班会补漏洞）</v>
+      </c>
+      <c r="D106" t="str">
+        <v>规则审视（1节班会补漏洞）</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>CS_RX_26</v>
+      </c>
+      <c r="B107" t="str">
+        <v>4</v>
+      </c>
+      <c r="C107" t="str">
+        <v>班主任自我复盘（3天内，复盘卡）</v>
+      </c>
+      <c r="D107" t="str">
+        <v>班主任自我复盘（3天内，复盘卡）</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>CS_RX_27</v>
+      </c>
+      <c r="B108" t="str">
+        <v>1</v>
+      </c>
+      <c r="C108" t="str">
+        <v>红旗清单判定风险等级（红/橙/黄/绿）</v>
+      </c>
+      <c r="D108" t="str">
+        <v>红旗清单判定风险等级（红/橙/黄/绿）</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>CS_RX_27</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2</v>
+      </c>
+      <c r="C109" t="str">
+        <v>红/橙级转介学校心理专业</v>
+      </c>
+      <c r="D109" t="str">
+        <v>红/橙级转介学校心理专业</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>CS_RX_27</v>
+      </c>
+      <c r="B110" t="str">
+        <v>3</v>
+      </c>
+      <c r="C110" t="str">
+        <v>保护性因素降级评估</v>
+      </c>
+      <c r="D110" t="str">
+        <v>保护性因素降级评估</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>CS_RX_27</v>
+      </c>
+      <c r="B111" t="str">
+        <v>4</v>
+      </c>
+      <c r="C111" t="str">
+        <v>家校沟通协作</v>
+      </c>
+      <c r="D111" t="str">
+        <v>家校沟通协作</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>CS_RX_28</v>
+      </c>
+      <c r="B112" t="str">
+        <v>1</v>
+      </c>
+      <c r="C112" t="str">
+        <v>停（安全隔开，移除危险源）</v>
+      </c>
+      <c r="D112" t="str">
+        <v>停（安全隔开，移除危险源）</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>CS_RX_28</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2</v>
+      </c>
+      <c r="C113" t="str">
+        <v>听（共情倾听，不评判）</v>
+      </c>
+      <c r="D113" t="str">
+        <v>听（共情倾听，不评判）</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>CS_RX_28</v>
+      </c>
+      <c r="B114" t="str">
+        <v>3</v>
+      </c>
+      <c r="C114" t="str">
+        <v>析-选（EQ四步：标情绪-析需求-选行动）</v>
+      </c>
+      <c r="D114" t="str">
+        <v>析-选（EQ四步：标情绪-析需求-选行动）</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>CS_RX_29</v>
+      </c>
+      <c r="B115" t="str">
+        <v>1</v>
+      </c>
+      <c r="C115" t="str">
+        <v>日常反馈（73855：70%积极+30%待改进）</v>
+      </c>
+      <c r="D115" t="str">
+        <v>日常反馈（73855：70%积极+30%待改进）</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>CS_RX_29</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2</v>
+      </c>
+      <c r="C116" t="str">
+        <v>投诉处理（先跟后带+意义换框）</v>
+      </c>
+      <c r="D116" t="str">
+        <v>投诉处理（先跟后带+意义换框）</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>CS_RX_29</v>
+      </c>
+      <c r="B117" t="str">
+        <v>3</v>
+      </c>
+      <c r="C117" t="str">
+        <v>结构化表达（事实-影响-建议）</v>
+      </c>
+      <c r="D117" t="str">
+        <v>结构化表达（事实-影响-建议）</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>CS_RX_30</v>
+      </c>
+      <c r="B118" t="str">
+        <v>1</v>
+      </c>
+      <c r="C118" t="str">
+        <v>从『情况通报』升级为『共同叙事』</v>
+      </c>
+      <c r="D118" t="str">
+        <v>从『情况通报』升级为『共同叙事』</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>CS_RX_30</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2</v>
+      </c>
+      <c r="C119" t="str">
+        <v>4形式（全体/小组/工作坊/学生主导）</v>
+      </c>
+      <c r="D119" t="str">
+        <v>4形式（全体/小组/工作坊/学生主导）</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>CS_RX_30</v>
+      </c>
+      <c r="B120" t="str">
+        <v>3</v>
+      </c>
+      <c r="C120" t="str">
+        <v>先展示非学业成就再谈学业</v>
+      </c>
+      <c r="D120" t="str">
+        <v>先展示非学业成就再谈学业</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>CS_RX_31</v>
+      </c>
+      <c r="B121" t="str">
+        <v>1</v>
+      </c>
+      <c r="C121" t="str">
+        <v>个别家访（针对需额外支持学生）</v>
+      </c>
+      <c r="D121" t="str">
+        <v>个别家访（针对需额外支持学生）</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>CS_RX_31</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2</v>
+      </c>
+      <c r="C122" t="str">
+        <v>家长工作坊（每学期1次主题技能）</v>
+      </c>
+      <c r="D122" t="str">
+        <v>家长工作坊（每学期1次主题技能）</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>CS_RX_31</v>
+      </c>
+      <c r="B123" t="str">
+        <v>3</v>
+      </c>
+      <c r="C123" t="str">
+        <v>降低门槛（把『参会』改为『群里回个表情』）</v>
+      </c>
+      <c r="D123" t="str">
+        <v>降低门槛（把『参会』改为『群里回个表情』）</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J123"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2018,30 +7904,76 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_06</v>
       </c>
       <c r="B2" t="str">
-        <v>冲突涉及肢体伤害或欺凌</v>
+        <v>冲突涉及欺凌或安全事件</v>
       </c>
       <c r="C2" t="str">
         <v>block</v>
       </c>
       <c r="D2" t="str">
-        <v>涉及安全事件须优先启动应急流程而非同伴调解</v>
+        <v>欺凌/安全事件须启动危机响应流程而非同伴调解</v>
       </c>
       <c r="E2" t="str">
-        <v>启动校园安全应急预案并通知年级组长</v>
+        <v>启动心理风险A-E响应SOP并上报学校</v>
       </c>
       <c r="F2" t="str">
         <v>班主任</v>
       </c>
       <c r="G2" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A级（安全事件）出现自伤/伤他行为</v>
+      </c>
+      <c r="C3" t="str">
+        <v>block</v>
+      </c>
+      <c r="D3" t="str">
+        <v>A级须24小时内学校+公安+心理转介</v>
+      </c>
+      <c r="E3" t="str">
+        <v>立即联系学校危机响应组并同步公安/医疗</v>
+      </c>
+      <c r="F3" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="G3" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CS_RX_28</v>
+      </c>
+      <c r="B4" t="str">
+        <v>存在自伤/伤他风险</v>
+      </c>
+      <c r="C4" t="str">
+        <v>block</v>
+      </c>
+      <c r="D4" t="str">
+        <v>情绪急救只处理情绪，安全风险须立即启动A-E响应</v>
+      </c>
+      <c r="E4" t="str">
+        <v>启动心理风险A-E响应SOP并上报</v>
+      </c>
+      <c r="F4" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="G4" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>